--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1426,6 +1426,158 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>45.136.131.32:8445</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>750.2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>38.34.179.14:8450</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>707.72</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>91.121.63.51:1080</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>397.61</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>65.108.203.36:18080</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1496.94</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>thespeedx_socks4</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2434,6 +2586,158 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>45.136.131.32:8445</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>750.2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>38.34.179.14:8450</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>707.72</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>91.121.63.51:1080</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>397.61</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>65.108.203.36:18080</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1496.94</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>thespeedx_socks4</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3074,6 +3378,46 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>45.136.131.32:8445</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>750.2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,6 +3514,46 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>неизвестен</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>38.34.179.14:8450</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>707.72</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:00:28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -3250,55 +3634,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26T14:59:47.591824</t>
+          <t>2026-03-26T17:00:28.317203</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007692307692307693</v>
+        <v>0.02272727272727273</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26T15:28:17.318126</t>
+          <t>2026-03-26T14:59:47.591824</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>14.88372093023256</v>
+        <v>0.007692307692307693</v>
       </c>
     </row>
     <row r="5">
@@ -3311,21 +3695,21 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-26T14:57:54.504793</t>
+          <t>2026-03-26T17:00:28.317872</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G5" t="n">
-        <v>2478.317829457364</v>
+        <v>0.007692307692307693</v>
       </c>
     </row>
     <row r="6">
@@ -3469,7 +3853,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -3479,7 +3863,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -3489,7 +3873,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3499,7 +3883,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3509,7 +3893,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3539,7 +3923,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -3550,7 +3934,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T15:28:17</t>
+          <t>2026-03-26T17:00:28</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,6 +1578,202 @@
       <c r="H30" t="inlineStr">
         <is>
           <t>thespeedx_socks4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>38.145.208.209:8444</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>38.34.179.27:8451</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>120.92.212.16:7890</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>966.12</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>38.34.179.162:8451</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>999.65</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>163.227.149.135:8080</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>2607.59</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2738,6 +2934,202 @@
       <c r="H30" t="inlineStr">
         <is>
           <t>thespeedx_socks4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>38.145.208.209:8444</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>38.34.179.27:8451</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>120.92.212.16:7890</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>966.12</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>38.34.179.162:8451</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>999.65</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>163.227.149.135:8080</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>2607.59</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
@@ -2864,7 +3256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3418,6 +3810,46 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>38.34.179.27:8451</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3554,6 +3986,86 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>38.145.208.209:8444</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>38.34.179.162:8451</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>999.65</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:05:06</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
@@ -3688,55 +4200,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>thespeedx_socks4</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-26T17:00:28.317872</t>
+          <t>2026-03-26T17:05:06.378832</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007692307692307693</v>
+        <v>0.03731343283582089</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>thespeedx_socks4</t>
         </is>
       </c>
       <c r="B6" t="b">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-26T14:57:54.514770</t>
+          <t>2026-03-26T17:00:28.317872</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
-        <v>1824.426356589147</v>
+        <v>0.007692307692307693</v>
       </c>
     </row>
     <row r="7">
@@ -3853,7 +4365,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -3863,7 +4375,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -3873,7 +4385,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3883,7 +4395,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -3893,7 +4405,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3923,7 +4435,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -3934,7 +4446,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T17:00:28</t>
+          <t>2026-03-26T17:05:06</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -4268,11 +4268,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-26T14:57:54.529134</t>
+          <t>2026-03-26T17:17:20.287448</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
         <v>1801</v>
@@ -4295,14 +4295,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-26T14:57:54.718788</t>
+          <t>2026-03-26T17:17:20.702123</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G8" t="n">
-        <v>15.04651162790698</v>
+        <v>15.06153846153846</v>
       </c>
     </row>
     <row r="9">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-26T14:57:54.779874</t>
+          <t>2026-03-26T17:17:20.924234</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G9" t="n">
-        <v>97.79069767441861</v>
+        <v>97.72307692307692</v>
       </c>
     </row>
   </sheetData>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1774,6 +1774,194 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>106.75.15.167:7890</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>992.76</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>89.208.106.138:10808</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>618.41</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>54.36.117.30:3128</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38.145.208.242:8451</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1962.5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>201.182.85.12:999</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>2105.99</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3130,6 +3318,194 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>106.75.15.167:7890</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>992.76</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>89.208.106.138:10808</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>618.41</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>54.36.117.30:3128</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38.145.208.242:8451</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1962.5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>201.182.85.12:999</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>2105.99</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3850,6 +4226,46 @@
       <c r="H15" t="inlineStr">
         <is>
           <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>38.145.208.242:8451</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1962.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -3864,7 +4280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4066,6 +4482,82 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>thespeedx_socks5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>89.208.106.138:10808</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>618.41</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>54.36.117.30:3128</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:22:48</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -4153,21 +4645,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26T17:00:28.317203</t>
+          <t>2026-03-26T17:22:48.707950</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="4">
@@ -4180,21 +4672,21 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26T14:59:47.591824</t>
+          <t>2026-03-26T17:22:48.710316</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007692307692307693</v>
+        <v>0.02255639097744361</v>
       </c>
     </row>
     <row r="5">
@@ -4365,7 +4857,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -4375,7 +4867,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -4385,7 +4877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4395,7 +4887,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -4405,7 +4897,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -4435,7 +4927,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4446,7 +4938,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T17:05:06</t>
+          <t>2026-03-26T17:22:48</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,6 +1960,154 @@
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>181.78.194.249:999</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>2975.85</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>194.67.99.223:1080</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>532.0700000000001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>222.184.48.251:22222</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>1453.28</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>13.36.243.194:9899</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>482.25</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -1976,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3504,6 +3652,154 @@
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>181.78.194.249:999</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>2975.85</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>194.67.99.223:1080</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>532.0700000000001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>222.184.48.251:22222</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>1453.28</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>13.36.243.194:9899</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>482.25</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4280,7 +4576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4556,6 +4852,46 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>194.67.99.223:1080</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>532.0700000000001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:33:10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4638,55 +4974,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26T17:22:48.707950</t>
+          <t>2026-03-26T19:33:10.828732</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.05109489051094891</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26T17:22:48.710316</t>
+          <t>2026-03-26T17:22:48.707950</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02255639097744361</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="5">
@@ -4857,7 +5193,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -4867,7 +5203,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -4877,7 +5213,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -4887,7 +5223,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -4897,7 +5233,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4927,7 +5263,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -4938,7 +5274,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T17:22:48</t>
+          <t>2026-03-26T19:33:10</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2108,6 +2108,226 @@
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>38.194.246.34:999</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>2179.36</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>43.99.54.236:5555</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1074.84</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45.136.130.193:8444</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>1189.26</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1.1.213.177:8080</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>1717.97</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>103.30.29.115:20326</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>1989.71</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>149.40.26.240:8080</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>1114.89</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2124,7 +2344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3800,6 +4020,226 @@
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>38.194.246.34:999</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>2179.36</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>43.99.54.236:5555</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1074.84</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45.136.130.193:8444</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>1189.26</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1.1.213.177:8080</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>1717.97</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>103.30.29.115:20326</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>1989.71</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>149.40.26.240:8080</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>1114.89</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3928,7 +4368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4562,6 +5002,46 @@
       <c r="H16" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>43.99.54.236:5555</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1074.84</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:03:49</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -4981,21 +5461,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26T19:33:10.828732</t>
+          <t>2026-03-26T20:03:49.309042</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05109489051094891</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="4">
@@ -5008,21 +5488,21 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26T17:22:48.707950</t>
+          <t>2026-03-26T20:03:49.305928</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.0364963503649635</v>
       </c>
     </row>
     <row r="5">
@@ -5193,7 +5673,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -5203,7 +5683,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -5223,7 +5703,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -5263,7 +5743,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -5274,7 +5754,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T19:33:10</t>
+          <t>2026-03-26T20:03:49</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,162 @@
         </is>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>38.34.179.105:8449</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1028.65</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>38.145.208.240:8446</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>103.156.16.160:8080</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>1664.11</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>121.230.8.220:1080</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1168.11</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2344,7 +2500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,6 +4396,162 @@
         </is>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>38.34.179.105:8449</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1028.65</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>38.145.208.240:8446</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>103.156.16.160:8080</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>1664.11</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>121.230.8.220:1080</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1168.11</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4368,7 +4680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5040,6 +5352,86 @@
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>38.34.179.105:8449</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1028.65</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>38.145.208.240:8446</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-26 20:49:23</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -5431,52 +5823,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T15:28:17.311981</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>2026-03-26T20:49:23.265533</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>142</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.08450704225352113</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26T20:03:49.309042</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>140</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.07142857142857142</v>
-      </c>
+          <t>2026-03-26T15:28:17.311981</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5488,21 +5880,21 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26T20:03:49.305928</t>
+          <t>2026-03-26T20:49:23.264575</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0364963503649635</v>
+        <v>0.05714285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -5673,7 +6065,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -5683,7 +6075,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -5703,7 +6095,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -5743,7 +6135,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -5754,7 +6146,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T20:03:49</t>
+          <t>2026-03-26T20:49:23</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2484,154 @@
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>103.144.209.104:8715</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>2039.46</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>65.108.203.35:28080</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>941.98</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>38.34.179.40:8446</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>868.99</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>178.156.224.42:3128</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>1791.97</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2500,7 +2648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4552,6 +4700,154 @@
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>103.144.209.104:8715</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>2039.46</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>65.108.203.35:28080</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>941.98</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>38.34.179.40:8446</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>868.99</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>178.156.224.42:3128</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>1791.97</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4680,7 +4976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5434,6 +5730,46 @@
       <c r="H19" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>38.34.179.40:8446</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>868.99</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:20:07</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -5830,21 +6166,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T20:49:23.265533</t>
+          <t>2026-03-26T21:20:07.529775</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.1095890410958904</v>
       </c>
     </row>
     <row r="3">
@@ -6065,7 +6401,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -6075,7 +6411,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -6135,7 +6471,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -6146,7 +6482,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T20:49:23</t>
+          <t>2026-03-26T21:20:07</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,158 @@
         </is>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>38.34.183.234:8450</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1546.16</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>119.18.145.52:20326</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2234.12</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>103.40.226.126:26100</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>2866.2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>45.136.130.171:8445</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1172.53</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2648,7 +2800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4848,6 +5000,158 @@
         </is>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>38.34.183.234:8450</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1546.16</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>119.18.145.52:20326</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2234.12</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>103.40.226.126:26100</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>2866.2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>45.136.130.171:8445</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1172.53</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4976,7 +5280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5768,6 +6072,46 @@
         </is>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>38.34.183.234:8450</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1546.16</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5784,7 +6128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6100,6 +6444,46 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>45.136.130.171:8445</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1172.53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:51:01</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6166,21 +6550,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T21:20:07.529775</t>
+          <t>2026-03-26T21:51:01.217002</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1095890410958904</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -6401,7 +6785,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -6411,7 +6795,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -6421,7 +6805,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -6431,7 +6815,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -6441,7 +6825,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -6471,7 +6855,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -6482,7 +6866,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T21:20:07</t>
+          <t>2026-03-26T21:51:01</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,6 +2784,198 @@
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>187.49.176.141:8080</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>944.76</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>210.201.86.72:8080</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>858.39</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>101.6.65.26:10808</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1371.17</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>47.77.193.180:1080</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>103.84.95.54:7890</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1973.32</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2800,7 +2992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5152,6 +5344,198 @@
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>187.49.176.141:8080</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>944.76</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>210.201.86.72:8080</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>858.39</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>101.6.65.26:10808</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1371.17</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>47.77.193.180:1080</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>103.84.95.54:7890</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1973.32</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5280,7 +5664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6112,6 +6496,46 @@
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>103.84.95.54:7890</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1973.32</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6128,7 +6552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6484,6 +6908,46 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>47.77.193.180:1080</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:18:34</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6550,21 +7014,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T21:51:01.217002</t>
+          <t>2026-03-26T22:18:34.365517</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1612903225806452</v>
       </c>
     </row>
     <row r="3">
@@ -6785,7 +7249,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -6795,7 +7259,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -6805,7 +7269,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -6815,7 +7279,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6825,7 +7289,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -6855,7 +7319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6866,7 +7330,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T21:51:01</t>
+          <t>2026-03-26T22:18:34</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +2976,122 @@
         </is>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>38.145.220.102:8453</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2523.64</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>119.18.144.3:30226</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>1524.19</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5.104.87.17:8051</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1109.17</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2992,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5536,6 +5652,122 @@
         </is>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>38.145.220.102:8453</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2523.64</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>119.18.144.3:30226</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>1524.19</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5.104.87.17:8051</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1109.17</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5664,7 +5896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6536,6 +6768,86 @@
         </is>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>38.145.220.102:8453</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2523.64</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5.104.87.17:8051</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1109.17</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:53:06</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7014,21 +7326,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T22:18:34.365517</t>
+          <t>2026-03-26T22:53:06.002454</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1772151898734177</v>
       </c>
     </row>
     <row r="3">
@@ -7249,7 +7561,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -7259,7 +7571,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -7279,7 +7591,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -7319,7 +7631,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -7330,7 +7642,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T22:18:34</t>
+          <t>2026-03-26T22:53:06</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3092,6 +3092,162 @@
         </is>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>163.5.128.37:14270</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>678.8200000000001</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>150.107.140.238:3128</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1976.51</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>38.145.208.244:8448</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>198.44</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>167.103.144.127:8800</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>724.85</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3108,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5768,6 +5924,162 @@
         </is>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>163.5.128.37:14270</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>678.8200000000001</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>150.107.140.238:3128</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1976.51</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>38.145.208.244:8448</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>198.44</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>167.103.144.127:8800</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>724.85</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5896,7 +6208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6848,6 +7160,126 @@
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>150.107.140.238:3128</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1976.51</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>38.145.208.244:8448</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>198.44</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>167.103.144.127:8800</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>724.85</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:28:37</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7326,21 +7758,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T22:53:06.002454</t>
+          <t>2026-03-26T23:28:37.559337</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1772151898734177</v>
+        <v>0.1975308641975309</v>
       </c>
     </row>
     <row r="3">
@@ -7561,7 +7993,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -7571,7 +8003,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -7591,7 +8023,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -7631,7 +8063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -7642,7 +8074,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T22:53:06</t>
+          <t>2026-03-26T23:28:37</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3248,6 +3248,158 @@
         </is>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>203.205.49.2:10014</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>2999.7</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>157.20.253.43:8989</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>1909.51</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>713.54</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>137.220.150.170:6005</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2806.75</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3264,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6080,6 +6232,158 @@
         </is>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>203.205.49.2:10014</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>2999.7</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>157.20.253.43:8989</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>1909.51</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>713.54</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>137.220.150.170:6005</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2806.75</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7296,7 +7600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7692,6 +7996,46 @@
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>713.54</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:59:58</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7758,21 +8102,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T23:28:37.559337</t>
+          <t>2026-03-26T23:59:58.552534</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1975308641975309</v>
+        <v>0.2168674698795181</v>
       </c>
     </row>
     <row r="3">
@@ -7993,7 +8337,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -8003,7 +8347,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -8013,7 +8357,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -8023,7 +8367,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -8033,7 +8377,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -8063,7 +8407,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -8074,7 +8418,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T23:28:37</t>
+          <t>2026-03-26T23:59:58</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3400,6 +3400,86 @@
         </is>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16.78.119.130:443</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1063.16</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>15.204.151.149:3128</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3416,7 +3496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6384,6 +6464,86 @@
         </is>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16.78.119.130:443</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1063.16</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>15.204.151.149:3128</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6512,7 +6672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7584,6 +7744,46 @@
         </is>
       </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15.204.151.149:3128</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-03-27 03:25:45</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -8102,21 +8302,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-26T23:59:58.552534</t>
+          <t>2026-03-27T03:25:45.664910</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2168674698795181</v>
+        <v>0.2261904761904762</v>
       </c>
     </row>
     <row r="3">
@@ -8337,7 +8537,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -8347,7 +8547,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -8407,7 +8607,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -8418,7 +8618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T23:59:58</t>
+          <t>2026-03-27T03:25:45</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3480,6 +3480,198 @@
         </is>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>195.123.213.129:1080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2800.34</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>120.92.212.16:8890</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>953.05</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1081</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>525.4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>57.128.188.167:8188</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>1923.01</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>161.49.90.70:1337</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>2327.23</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3496,7 +3688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6544,6 +6736,198 @@
         </is>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>195.123.213.129:1080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2800.34</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>120.92.212.16:8890</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>953.05</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1081</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>525.4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>57.128.188.167:8188</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>1923.01</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>161.49.90.70:1337</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>2327.23</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6672,7 +7056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7786,6 +8170,46 @@
       <c r="H28" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>195.123.213.129:1080</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2800.34</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:23:21</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -8302,72 +8726,72 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T03:25:45.664910</t>
+          <t>2026-03-27T05:23:21.647781</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.2352941176470588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26T15:28:17.311981</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>2026-03-27T05:23:21.645161</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26T20:49:23.264575</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>140</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05714285714285714</v>
-      </c>
+          <t>2026-03-26T15:28:17.311981</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8537,7 +8961,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -8547,7 +8971,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -8567,7 +8991,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -8607,7 +9031,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -8618,7 +9042,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T03:25:45</t>
+          <t>2026-03-27T05:23:21</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3672,82 @@
         </is>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8126</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>🇷🇺 Россия</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2800.94</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>59.46.216.131:30001</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>1972.41</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3688,7 +3764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6928,6 +7004,82 @@
         </is>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8126</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>🇷🇺 Россия</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2800.94</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>59.46.216.131:30001</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>1972.41</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7000,7 +7152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7042,6 +7194,46 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8126</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🇷🇺 Россия</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2800.94</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:45:05</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -8726,21 +8918,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T05:23:21.647781</t>
+          <t>2026-03-27T06:45:05.104088</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.239766081871345</v>
       </c>
     </row>
     <row r="3">
@@ -8753,21 +8945,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T05:23:21.645161</t>
+          <t>2026-03-27T06:45:05.102538</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -8961,7 +9153,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -8971,7 +9163,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -9031,7 +9223,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -9042,7 +9234,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T05:23:21</t>
+          <t>2026-03-27T06:45:05</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,6 +3748,162 @@
         </is>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>38.34.179.161:8448</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>478.19</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>45.149.92.147:5001</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1050.12</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>114.130.153.46:58080</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>1739.08</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>160.250.134.143:3128</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1150.45</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3764,7 +3920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7080,6 +7236,162 @@
         </is>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>38.34.179.161:8448</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>478.19</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>45.149.92.147:5001</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1050.12</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>114.130.153.46:58080</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>1739.08</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>160.250.134.143:3128</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1150.45</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7248,7 +7560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8402,6 +8714,46 @@
       <c r="H29" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>160.250.134.143:3128</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1150.45</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8854,6 +9206,46 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>38.34.179.161:8448</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>478.19</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-27 07:48:24</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -8918,21 +9310,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T06:45:05.104088</t>
+          <t>2026-03-27T07:48:24.140844</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G2" t="n">
-        <v>0.239766081871345</v>
+        <v>0.2528735632183908</v>
       </c>
     </row>
     <row r="3">
@@ -8945,21 +9337,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T06:45:05.102538</t>
+          <t>2026-03-27T07:48:24.135166</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.0958904109589041</v>
       </c>
     </row>
     <row r="4">
@@ -9153,7 +9545,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -9163,7 +9555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -9173,7 +9565,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -9183,7 +9575,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -9193,7 +9585,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -9223,7 +9615,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -9234,7 +9626,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T06:45:05</t>
+          <t>2026-03-27T07:48:24</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3904,6 +3904,82 @@
         </is>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8124</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>1131.85</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>137.220.150.152:6005</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2583.1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3920,7 +3996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7392,6 +7468,82 @@
         </is>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8124</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>1131.85</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>137.220.150.152:6005</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2583.1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9310,21 +9462,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T07:48:24.140844</t>
+          <t>2026-03-27T08:36:11.783012</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2528735632183908</v>
+        <v>0.2571428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -9337,21 +9489,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T07:48:24.135166</t>
+          <t>2026-03-27T08:36:11.781100</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.1020408163265306</v>
       </c>
     </row>
     <row r="4">
@@ -9545,7 +9697,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -9555,7 +9707,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -9615,7 +9767,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -9626,7 +9778,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T07:48:24</t>
+          <t>2026-03-27T08:36:11</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3980,6 +3980,42 @@
         </is>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>163.5.128.129:14270</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>2272.15</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:37:29</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:37:29</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -3996,7 +4032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7544,6 +7580,42 @@
         </is>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>163.5.128.129:14270</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>2272.15</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:37:29</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:37:29</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9462,21 +9534,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T08:36:11.783012</t>
+          <t>2026-03-27T09:37:29.585114</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2613636363636364</v>
       </c>
     </row>
     <row r="3">
@@ -9697,7 +9769,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -9707,7 +9779,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -9767,7 +9839,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -9778,7 +9850,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T08:36:11</t>
+          <t>2026-03-27T09:37:29</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4016,6 +4016,42 @@
         </is>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>120.92.211.211:7890</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>2444.98</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:31:30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:31:30</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4032,7 +4068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7616,6 +7652,42 @@
         </is>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>120.92.211.211:7890</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>2444.98</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:31:30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:31:30</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9534,21 +9606,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T09:37:29.585114</t>
+          <t>2026-03-27T10:31:30.075994</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2613636363636364</v>
+        <v>0.2655367231638418</v>
       </c>
     </row>
     <row r="3">
@@ -9769,7 +9841,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -9779,7 +9851,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -9839,7 +9911,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -9850,7 +9922,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T09:37:29</t>
+          <t>2026-03-27T10:31:30</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4052,6 +4052,42 @@
         </is>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>43.250.54.139:60000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>1492.43</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:26:50</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:26:50</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4068,7 +4104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7688,6 +7724,42 @@
         </is>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>43.250.54.139:60000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>1492.43</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:26:50</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:26:50</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9606,21 +9678,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T10:31:30.075994</t>
+          <t>2026-03-27T11:26:50.407037</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2655367231638418</v>
+        <v>0.2696629213483146</v>
       </c>
     </row>
     <row r="3">
@@ -9841,7 +9913,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -9851,7 +9923,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -9911,7 +9983,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -9922,7 +9994,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T10:31:30</t>
+          <t>2026-03-27T11:26:50</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4088,6 +4088,82 @@
         </is>
       </c>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>82.146.58.184:1080</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>🇷🇺 Россия</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1087.01</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>187.251.224.167:8081</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>2974.85</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4104,7 +4180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7760,6 +7836,82 @@
         </is>
       </c>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>82.146.58.184:1080</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>🇷🇺 Россия</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1087.01</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>187.251.224.167:8081</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>2974.85</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -7832,7 +7984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7912,6 +8064,46 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>82.146.58.184:1080</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🇷🇺 Россия</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1087.01</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:05:22</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -9678,21 +9870,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T11:26:50.407037</t>
+          <t>2026-03-27T12:05:22.340555</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2696629213483146</v>
+        <v>0.2737430167597765</v>
       </c>
     </row>
     <row r="3">
@@ -9705,21 +9897,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T08:36:11.781100</t>
+          <t>2026-03-27T12:05:22.338434</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1020408163265306</v>
+        <v>0.1081081081081081</v>
       </c>
     </row>
     <row r="4">
@@ -9913,7 +10105,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -9923,7 +10115,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -9943,7 +10135,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -9983,7 +10175,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -9994,7 +10186,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T11:26:50</t>
+          <t>2026-03-27T12:05:22</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4164,6 +4164,42 @@
         </is>
       </c>
       <c r="H98" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>113.11.36.205:30226</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>1097.82</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-27 13:41:52</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-03-27 13:41:52</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4180,7 +4216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7912,6 +7948,42 @@
         </is>
       </c>
       <c r="H98" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>113.11.36.205:30226</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>1097.82</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-27 13:41:52</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-03-27 13:41:52</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9870,21 +9942,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T12:05:22.340555</t>
+          <t>2026-03-27T13:41:52.923378</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2737430167597765</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="3">
@@ -10105,7 +10177,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -10115,7 +10187,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -10175,7 +10247,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -10186,7 +10258,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T12:05:22</t>
+          <t>2026-03-27T13:41:52</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4200,6 +4200,202 @@
         </is>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>185.114.73.2:1080</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>🇪🇺 Европа</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1596.77</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>45.136.130.191:8453</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1082</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>531.15</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>38.34.179.6:8449</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>720.92</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>167.71.196.28:8080</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="n">
+        <v>1125.33</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4216,7 +4412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7984,6 +8180,202 @@
         </is>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>185.114.73.2:1080</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>🇪🇺 Европа</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1596.77</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>45.136.130.191:8453</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1082</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>531.15</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>38.34.179.6:8449</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>720.92</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>167.71.196.28:8080</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="n">
+        <v>1125.33</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -8192,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9384,6 +9776,82 @@
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>38.34.179.6:8449</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>720.92</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>167.71.196.28:8080</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1125.33</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9400,7 +9868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9876,6 +10344,46 @@
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>45.136.130.191:8453</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-27 14:38:03</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -9942,21 +10450,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T13:41:52.923378</t>
+          <t>2026-03-27T14:38:03.397046</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -9969,21 +10477,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T12:05:22.338434</t>
+          <t>2026-03-27T14:38:03.393809</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1081081081081081</v>
+        <v>0.1258278145695364</v>
       </c>
     </row>
     <row r="4">
@@ -10177,7 +10685,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -10187,7 +10695,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -10197,7 +10705,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -10207,7 +10715,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -10217,7 +10725,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -10247,7 +10755,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -10258,7 +10766,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T13:41:52</t>
+          <t>2026-03-27T14:38:03</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4396,6 +4396,42 @@
         </is>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>45.175.59.2:61950</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="n">
+        <v>2286.16</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:32:32</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:32:32</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4412,7 +4448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8376,6 +8412,42 @@
         </is>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>45.175.59.2:61950</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="n">
+        <v>2286.16</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:32:32</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:32:32</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -10450,21 +10522,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T14:38:03.397046</t>
+          <t>2026-03-27T15:32:32.341806</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2896174863387978</v>
       </c>
     </row>
     <row r="3">
@@ -10685,7 +10757,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
@@ -10695,7 +10767,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -10755,7 +10827,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -10766,7 +10838,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T14:38:03</t>
+          <t>2026-03-27T15:32:32</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4432,6 +4432,86 @@
         </is>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>38.145.218.104:8449</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2074.82</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>222.184.48.242:22222</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2167.52</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4448,7 +4528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8448,6 +8528,86 @@
         </is>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>38.145.218.104:8449</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2074.82</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>222.184.48.242:22222</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2167.52</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -8656,7 +8816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9926,6 +10086,46 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>38.145.218.104:8449</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2074.82</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:32:08</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -10522,21 +10722,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T15:32:32.341806</t>
+          <t>2026-03-27T16:32:08.921490</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2896174863387978</v>
+        <v>0.2934782608695652</v>
       </c>
     </row>
     <row r="3">
@@ -10549,21 +10749,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T14:38:03.393809</t>
+          <t>2026-03-27T16:32:08.919776</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1258278145695364</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="4">
@@ -10757,7 +10957,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -10767,7 +10967,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -10827,7 +11027,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -10838,7 +11038,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T15:32:32</t>
+          <t>2026-03-27T16:32:08</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4514,6 +4514,86 @@
       <c r="H107" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>38.145.208.189:8449</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>38.145.220.188:8452</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1612.94</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8610,6 +8690,86 @@
       <c r="H107" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>38.145.208.189:8449</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>38.145.220.188:8452</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1612.94</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10124,6 +10284,46 @@
         </is>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>38.145.220.188:8452</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1612.94</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -10140,7 +10340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10656,6 +10856,46 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>38.145.208.189:8449</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:31:32</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -10749,21 +10989,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T16:32:08.919776</t>
+          <t>2026-03-27T17:31:32.342241</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G3" t="n">
-        <v>0.131578947368421</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="4">
@@ -10957,7 +11197,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
@@ -10967,7 +11207,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
@@ -10977,7 +11217,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -10987,7 +11227,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -10997,7 +11237,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -11027,7 +11267,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -11038,7 +11278,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T16:32:08</t>
+          <t>2026-03-27T17:31:32</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4594,6 +4594,118 @@
       <c r="H109" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8127</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>2751.32</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>38.34.179.173:8452</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1713.91</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>195.158.8.123:3128</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>2631.75</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8770,6 +8882,118 @@
       <c r="H109" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8127</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>2751.32</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>38.34.179.173:8452</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1713.91</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>195.158.8.123:3128</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>2631.75</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -8976,7 +9200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10324,6 +10548,46 @@
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>38.34.179.173:8452</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1713.91</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:32:06</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -10962,21 +11226,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T16:32:08.921490</t>
+          <t>2026-03-27T18:32:06.856309</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2934782608695652</v>
+        <v>0.2972972972972973</v>
       </c>
     </row>
     <row r="3">
@@ -10989,21 +11253,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T17:31:32.342241</t>
+          <t>2026-03-27T18:32:06.854682</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="4">
@@ -11197,7 +11461,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3">
@@ -11207,7 +11471,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -11227,7 +11491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -11267,7 +11531,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -11278,7 +11542,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T17:31:32</t>
+          <t>2026-03-27T18:32:06</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4704,6 +4704,42 @@
         </is>
       </c>
       <c r="H112" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>165.16.27.42:1981</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>2549.81</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:26:37</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:26:37</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4720,7 +4756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8992,6 +9028,42 @@
         </is>
       </c>
       <c r="H112" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>165.16.27.42:1981</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>2549.81</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:26:37</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:26:37</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -11226,21 +11298,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T18:32:06.856309</t>
+          <t>2026-03-27T19:26:37.354160</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.3010752688172043</v>
       </c>
     </row>
     <row r="3">
@@ -11461,7 +11533,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
@@ -11471,7 +11543,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4">
@@ -11531,7 +11603,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -11542,7 +11614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T18:32:06</t>
+          <t>2026-03-27T19:26:37</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4740,6 +4740,114 @@
         </is>
       </c>
       <c r="H113" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>49.156.44.115:8080</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>2849.97</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>203.146.80.102:8080</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="n">
+        <v>1701.01</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>181.78.49.177:999</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="n">
+        <v>2577.3</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4756,7 +4864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9064,6 +9172,114 @@
         </is>
       </c>
       <c r="H113" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>49.156.44.115:8080</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>2849.97</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>203.146.80.102:8080</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="n">
+        <v>1701.01</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>181.78.49.177:999</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="n">
+        <v>2577.3</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:59:56</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -11298,21 +11514,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T19:26:37.354160</t>
+          <t>2026-03-27T19:59:56.956951</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3010752688172043</v>
+        <v>0.3085106382978723</v>
       </c>
     </row>
     <row r="3">
@@ -11325,21 +11541,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T18:32:06.854682</t>
+          <t>2026-03-27T19:59:56.953130</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1592356687898089</v>
       </c>
     </row>
     <row r="4">
@@ -11533,7 +11749,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -11543,7 +11759,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4">
@@ -11603,7 +11819,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -11614,7 +11830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T19:26:37</t>
+          <t>2026-03-27T19:59:56</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4848,6 +4848,154 @@
         </is>
       </c>
       <c r="H116" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>185.76.240.165:10001</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="n">
+        <v>1217.74</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38.145.208.220:8451</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1092.47</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>185.76.241.111:10001</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="n">
+        <v>1059.19</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>147.75.34.105:443</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>2085.95</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4864,7 +5012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9280,6 +9428,154 @@
         </is>
       </c>
       <c r="H116" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>185.76.240.165:10001</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="n">
+        <v>1217.74</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38.145.208.220:8451</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1092.47</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>185.76.241.111:10001</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="n">
+        <v>1059.19</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>147.75.34.105:443</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>2085.95</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -9488,7 +9784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10876,6 +11172,118 @@
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>185.76.240.165:10001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>1217.74</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>38.145.208.220:8451</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1092.47</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>185.76.241.111:10001</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>1059.19</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-03-27 20:52:29</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -11514,21 +11922,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T19:59:56.956951</t>
+          <t>2026-03-27T20:52:29.059938</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.3121693121693122</v>
       </c>
     </row>
     <row r="3">
@@ -11541,21 +11949,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T19:59:56.953130</t>
+          <t>2026-03-27T20:52:29.058072</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1592356687898089</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="4">
@@ -11749,7 +12157,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3">
@@ -11759,7 +12167,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -11779,7 +12187,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -11819,7 +12227,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -11830,7 +12238,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T19:59:56</t>
+          <t>2026-03-27T20:52:29</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4996,6 +4996,42 @@
         </is>
       </c>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>65.21.201.149:8080</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="n">
+        <v>1732.18</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-27 21:29:12</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-03-27 21:29:12</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5012,7 +5048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9576,6 +9612,42 @@
         </is>
       </c>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>65.21.201.149:8080</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="n">
+        <v>1732.18</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-27 21:29:12</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-03-27 21:29:12</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -11922,21 +11994,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T20:52:29.059938</t>
+          <t>2026-03-27T21:29:12.133032</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3121693121693122</v>
+        <v>0.3157894736842105</v>
       </c>
     </row>
     <row r="3">
@@ -12157,7 +12229,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -12167,7 +12239,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -12227,7 +12299,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -12238,7 +12310,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T20:52:29</t>
+          <t>2026-03-27T21:29:12</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5032,6 +5032,222 @@
         </is>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>200.69.83.203:999</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="n">
+        <v>1168.51</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>185.225.40.236:8080</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>1032.74</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>185.76.240.150:10001</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>1615.68</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>223.205.57.57:8080</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="n">
+        <v>1728.81</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>122.185.198.242:7999</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>2636.64</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>103.102.14.51:1111</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>2687.42</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5048,7 +5264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9648,6 +9864,222 @@
         </is>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>200.69.83.203:999</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="n">
+        <v>1168.51</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>185.225.40.236:8080</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>1032.74</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>185.76.240.150:10001</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>1615.68</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>223.205.57.57:8080</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="n">
+        <v>1728.81</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>122.185.198.242:7999</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>2636.64</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>103.102.14.51:1111</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>2687.42</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:00:25</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -11994,21 +12426,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T21:29:12.133032</t>
+          <t>2026-03-27T22:00:25.302661</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3264248704663212</v>
       </c>
     </row>
     <row r="3">
@@ -12021,21 +12453,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T20:52:29.058072</t>
+          <t>2026-03-27T22:00:25.297202</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.175</v>
+        <v>0.1901840490797546</v>
       </c>
     </row>
     <row r="4">
@@ -12229,7 +12661,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
@@ -12239,7 +12671,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
@@ -12299,7 +12731,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -12310,7 +12742,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T21:29:12</t>
+          <t>2026-03-27T22:00:25</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5250,6 +5250,326 @@
       <c r="H127" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>38.34.179.7:8448</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>482.52</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>38.34.179.36:8448</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2092.59</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>38.145.220.72:8446</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>391.86</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>38.145.208.164:8446</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>38.145.208.186:8446</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>393.32</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>45.136.130.167:8449</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1509.38</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>83.219.250.8:62920</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>458.11</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>38.145.218.104:8452</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10082,6 +10402,326 @@
       <c r="H127" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>38.34.179.7:8448</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>482.52</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>38.34.179.36:8448</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2092.59</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>38.145.220.72:8446</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>391.86</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>38.145.208.164:8446</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>38.145.208.186:8446</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>393.32</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>45.136.130.167:8449</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1509.38</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>83.219.250.8:62920</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>458.11</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>38.145.218.104:8452</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11788,6 +12428,246 @@
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38.34.179.7:8448</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>482.52</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38.34.179.36:8448</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2092.59</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>38.145.220.72:8446</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>391.86</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>38.145.208.164:8446</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>45.136.130.167:8449</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1509.38</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>38.145.218.104:8452</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -11804,7 +12684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12360,6 +13240,86 @@
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>38.145.208.186:8446</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>393.32</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>83.219.250.8:62920</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>458.11</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:48:03</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -12453,21 +13413,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T22:00:25.297202</t>
+          <t>2026-03-27T22:48:03.668391</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1901840490797546</v>
+        <v>0.2280701754385965</v>
       </c>
     </row>
     <row r="4">
@@ -12661,7 +13621,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
@@ -12671,7 +13631,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
@@ -12681,7 +13641,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -12691,7 +13651,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -12701,7 +13661,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -12731,7 +13691,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -12742,7 +13702,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T22:00:25</t>
+          <t>2026-03-27T22:48:03</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5570,6 +5570,42 @@
       <c r="H135" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>163.5.128.20:14270</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="n">
+        <v>1262.73</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:20:02</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:20:02</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10722,6 +10758,42 @@
       <c r="H135" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>163.5.128.20:14270</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="n">
+        <v>1262.73</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:20:02</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:20:02</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -13386,21 +13458,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T22:00:25.302661</t>
+          <t>2026-03-27T23:20:02.469221</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3264248704663212</v>
+        <v>0.3298969072164948</v>
       </c>
     </row>
     <row r="3">
@@ -13621,7 +13693,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
@@ -13631,7 +13703,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
@@ -13691,7 +13763,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -13702,7 +13774,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T22:48:03</t>
+          <t>2026-03-27T23:20:02</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5604,6 +5604,162 @@
         </is>
       </c>
       <c r="H136" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>38.145.218.210:8449</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>38.145.208.219:8450</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>38.145.208.167:8445</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>657.14</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>116.171.106.15:3443</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="n">
+        <v>1516.52</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5620,7 +5776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10792,6 +10948,162 @@
         </is>
       </c>
       <c r="H136" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>38.145.218.210:8449</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>38.145.208.219:8450</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>38.145.208.167:8445</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>657.14</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>116.171.106.15:3443</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="n">
+        <v>1516.52</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -12756,7 +13068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13392,6 +13704,126 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>38.145.218.210:8449</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>38.145.208.219:8450</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>38.145.208.167:8445</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>657.14</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:19</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -13458,21 +13890,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T23:20:02.469221</t>
+          <t>2026-03-27T23:50:19.220271</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3298969072164948</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -13485,21 +13917,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T22:48:03.668391</t>
+          <t>2026-03-27T23:50:19.218314</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2280701754385965</v>
+        <v>0.2413793103448276</v>
       </c>
     </row>
     <row r="4">
@@ -13693,7 +14125,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
@@ -13703,7 +14135,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -13713,7 +14145,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -13723,7 +14155,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -13733,7 +14165,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -13763,7 +14195,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -13774,7 +14206,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T23:20:02</t>
+          <t>2026-03-27T23:50:19</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5760,6 +5760,162 @@
         </is>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>38.145.208.234:8453</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>689.4400000000001</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>38.145.218.76:8451</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>384.97</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>38.34.179.30:8447</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>400.76</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>50.235.247.114:8085</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>2305.95</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5776,7 +5932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11104,6 +11260,162 @@
         </is>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>38.145.208.234:8453</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>689.4400000000001</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>38.145.218.76:8451</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>384.97</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>38.34.179.30:8447</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>400.76</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>50.235.247.114:8085</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>2305.95</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -11312,7 +11624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13052,6 +13364,86 @@
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>38.145.218.76:8451</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>384.97</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>38.34.179.30:8447</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>400.76</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -13068,7 +13460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13824,6 +14216,46 @@
         </is>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>38.145.208.234:8453</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>689.4400000000001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-28 03:45:15</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -13890,21 +14322,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-27T23:50:19.220271</t>
+          <t>2026-03-28T03:45:15.417856</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.336734693877551</v>
       </c>
     </row>
     <row r="3">
@@ -13917,21 +14349,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-27T23:50:19.218314</t>
+          <t>2026-03-28T03:45:15.415901</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.2542372881355932</v>
       </c>
     </row>
     <row r="4">
@@ -14125,7 +14557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -14135,7 +14567,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4">
@@ -14145,7 +14577,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -14155,7 +14587,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -14165,7 +14597,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -14195,7 +14627,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -14206,7 +14638,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-27T23:50:19</t>
+          <t>2026-03-28T03:45:15</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5916,6 +5916,158 @@
         </is>
       </c>
       <c r="H144" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>101.251.204.174:8080</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>1083.46</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>45.136.131.55:8453</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>893.27</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>190.12.150.244:999</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>2426.93</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>181.129.147.163:8080</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>2589.97</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5932,7 +6084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11416,6 +11568,158 @@
         </is>
       </c>
       <c r="H144" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>101.251.204.174:8080</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>1083.46</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>45.136.131.55:8453</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>893.27</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>190.12.150.244:999</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>2426.93</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>181.129.147.163:8080</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>2589.97</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -11624,7 +11928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13444,6 +13748,46 @@
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45.136.131.55:8453</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>893.27</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:14:59</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -14322,21 +14666,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T03:45:15.417856</t>
+          <t>2026-03-28T05:14:59.644042</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2" t="n">
-        <v>0.336734693877551</v>
+        <v>0.3401015228426396</v>
       </c>
     </row>
     <row r="3">
@@ -14349,21 +14693,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T03:45:15.415901</t>
+          <t>2026-03-28T05:14:59.641885</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2542372881355932</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -14557,7 +14901,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
@@ -14567,7 +14911,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
@@ -14627,7 +14971,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -14638,7 +14982,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T03:45:15</t>
+          <t>2026-03-28T05:14:59</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6068,6 +6068,78 @@
         </is>
       </c>
       <c r="H148" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>180.191.23.26:8081</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="n">
+        <v>2539</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>27.147.137.234:9108</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="n">
+        <v>2505.02</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6084,7 +6156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11720,6 +11792,78 @@
         </is>
       </c>
       <c r="H148" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>180.191.23.26:8081</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="n">
+        <v>2539</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>27.147.137.234:9108</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="n">
+        <v>2505.02</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-03-28 06:13:39</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -14666,21 +14810,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T05:14:59.644042</t>
+          <t>2026-03-28T06:13:39.592780</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3401015228426396</v>
+        <v>0.3467336683417085</v>
       </c>
     </row>
     <row r="3">
@@ -14901,7 +15045,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
@@ -14911,7 +15055,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
@@ -14971,7 +15115,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -14982,7 +15126,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T05:14:59</t>
+          <t>2026-03-28T06:13:39</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6140,6 +6140,42 @@
         </is>
       </c>
       <c r="H150" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>104.251.81.37:14270</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="n">
+        <v>2550.91</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:16:51</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:16:51</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6156,7 +6192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11864,6 +11900,42 @@
         </is>
       </c>
       <c r="H150" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>104.251.81.37:14270</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="n">
+        <v>2550.91</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:16:51</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:16:51</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -14810,21 +14882,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T06:13:39.592780</t>
+          <t>2026-03-28T07:16:51.137157</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3467336683417085</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="3">
@@ -15045,7 +15117,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -15055,7 +15127,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
@@ -15115,7 +15187,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -15126,7 +15198,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T06:13:39</t>
+          <t>2026-03-28T07:16:51</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6178,6 +6178,46 @@
       <c r="H151" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>64.181.240.152:3128</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>234.81</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:57:19</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:57:19</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11938,6 +11978,46 @@
       <c r="H151" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>64.181.240.152:3128</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>234.81</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:57:19</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:57:19</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14004,6 +14084,46 @@
         </is>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>64.181.240.152:3128</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>234.81</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:57:19</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-28 07:57:19</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -14909,21 +15029,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T05:14:59.641885</t>
+          <t>2026-03-28T07:57:19.689070</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2707182320441989</v>
       </c>
     </row>
     <row r="4">
@@ -15117,7 +15237,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -15127,7 +15247,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4">
@@ -15147,7 +15267,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -15187,7 +15307,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -15198,7 +15318,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T07:16:51</t>
+          <t>2026-03-28T07:57:19</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6216,6 +6216,46 @@
         </is>
       </c>
       <c r="H152" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>45.144.28.81:10808</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1608.33</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-28 08:52:54</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-03-28 08:52:54</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -6232,7 +6272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12016,6 +12056,46 @@
         </is>
       </c>
       <c r="H152" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>45.144.28.81:10808</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1608.33</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-28 08:52:54</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-03-28 08:52:54</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -15029,21 +15109,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T07:57:19.689070</t>
+          <t>2026-03-28T08:52:54.439285</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2707182320441989</v>
+        <v>0.2747252747252747</v>
       </c>
     </row>
     <row r="4">
@@ -15237,7 +15317,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -15247,7 +15327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
@@ -15307,7 +15387,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -15318,7 +15398,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T07:57:19</t>
+          <t>2026-03-28T08:52:54</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6258,6 +6258,42 @@
       <c r="H153" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>103.26.176.31:8080</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>2817.18</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-28 10:03:24</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-03-28 10:03:24</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12098,6 +12134,42 @@
       <c r="H153" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>103.26.176.31:8080</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>2817.18</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-28 10:03:24</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-03-28 10:03:24</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -15082,21 +15154,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T07:16:51.137157</t>
+          <t>2026-03-28T10:03:24.579821</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G2" t="n">
-        <v>0.35</v>
+        <v>0.3532338308457711</v>
       </c>
     </row>
     <row r="3">
@@ -15317,7 +15389,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
@@ -15327,7 +15399,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
@@ -15387,7 +15459,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -15398,7 +15470,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T08:52:54</t>
+          <t>2026-03-28T10:03:24</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6292,6 +6292,122 @@
         </is>
       </c>
       <c r="H154" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>45.144.232.5:11741</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1163.34</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>128.199.114.189:9090</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1574.69</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>190.54.100.74:8080</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>1698.92</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6308,7 +6424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12168,6 +12284,122 @@
         </is>
       </c>
       <c r="H154" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>45.144.232.5:11741</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1163.34</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>128.199.114.189:9090</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1574.69</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>190.54.100.74:8080</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>1698.92</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:16:32</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -15154,21 +15386,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T10:03:24.579821</t>
+          <t>2026-03-28T11:16:32.276362</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3532338308457711</v>
+        <v>0.3564356435643564</v>
       </c>
     </row>
     <row r="3">
@@ -15181,21 +15413,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T08:52:54.439285</t>
+          <t>2026-03-28T11:16:32.273858</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2747252747252747</v>
+        <v>0.2826086956521739</v>
       </c>
     </row>
     <row r="4">
@@ -15389,7 +15621,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
@@ -15399,7 +15631,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
@@ -15459,7 +15691,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -15470,7 +15702,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T10:03:24</t>
+          <t>2026-03-28T11:16:32</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6408,6 +6408,122 @@
         </is>
       </c>
       <c r="H157" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>128.199.254.13:9090</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>1356.18</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>168.63.153.150:3128</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1043.57</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>190.60.40.243:999</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="n">
+        <v>2638.71</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6424,7 +6540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12400,6 +12516,122 @@
         </is>
       </c>
       <c r="H157" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>128.199.254.13:9090</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>1356.18</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>168.63.153.150:3128</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1043.57</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>190.60.40.243:999</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="n">
+        <v>2638.71</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -12608,7 +12840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14510,6 +14742,46 @@
       <c r="H48" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>168.63.153.150:3128</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1043.57</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-28 11:46:50</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -15386,21 +15658,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T11:16:32.276362</t>
+          <t>2026-03-28T11:46:50.930648</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3564356435643564</v>
+        <v>0.3627450980392157</v>
       </c>
     </row>
     <row r="3">
@@ -15413,21 +15685,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T11:16:32.273858</t>
+          <t>2026-03-28T11:46:50.925706</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.2864864864864865</v>
       </c>
     </row>
     <row r="4">
@@ -15621,7 +15893,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -15631,7 +15903,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4">
@@ -15651,7 +15923,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -15691,7 +15963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -15702,7 +15974,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T11:16:32</t>
+          <t>2026-03-28T11:46:50</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6524,6 +6524,42 @@
         </is>
       </c>
       <c r="H160" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>103.124.136.251:8080</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="n">
+        <v>2921.96</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-28 12:23:58</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-03-28 12:23:58</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6540,7 +6576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12632,6 +12668,42 @@
         </is>
       </c>
       <c r="H160" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>103.124.136.251:8080</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="n">
+        <v>2921.96</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-28 12:23:58</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-03-28 12:23:58</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -15658,21 +15730,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T11:46:50.930648</t>
+          <t>2026-03-28T12:23:58.221391</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3627450980392157</v>
+        <v>0.3658536585365854</v>
       </c>
     </row>
     <row r="3">
@@ -15893,7 +15965,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -15903,7 +15975,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
@@ -15963,7 +16035,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -15974,7 +16046,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T11:46:50</t>
+          <t>2026-03-28T12:23:58</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6560,6 +6560,78 @@
         </is>
       </c>
       <c r="H161" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>45.174.56.21:999</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="n">
+        <v>2833.68</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>200.10.28.254:999</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="n">
+        <v>1407.51</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6576,7 +6648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12704,6 +12776,78 @@
         </is>
       </c>
       <c r="H161" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>45.174.56.21:999</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="n">
+        <v>2833.68</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>200.10.28.254:999</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="n">
+        <v>1407.51</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-03-28 13:32:09</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -15730,21 +15874,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T12:23:58.221391</t>
+          <t>2026-03-28T13:32:09.224735</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3719806763285024</v>
       </c>
     </row>
     <row r="3">
@@ -15965,7 +16109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
@@ -15975,7 +16119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
@@ -16035,7 +16179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -16046,7 +16190,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T12:23:58</t>
+          <t>2026-03-28T13:32:09</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6632,6 +6632,78 @@
         </is>
       </c>
       <c r="H163" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>221.202.27.194:10809</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="n">
+        <v>1009.62</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2.56.173.45:10808</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="n">
+        <v>1736.17</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6648,7 +6720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12848,6 +12920,78 @@
         </is>
       </c>
       <c r="H163" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>221.202.27.194:10809</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="n">
+        <v>1009.62</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2.56.173.45:10808</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="n">
+        <v>1736.17</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:06:59</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -15874,21 +16018,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T13:32:09.224735</t>
+          <t>2026-03-28T14:06:59.478933</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3719806763285024</v>
+        <v>0.3779904306220095</v>
       </c>
     </row>
     <row r="3">
@@ -16109,7 +16253,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -16119,7 +16263,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
@@ -16179,7 +16323,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -16190,7 +16334,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T13:32:09</t>
+          <t>2026-03-28T14:06:59</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6706,6 +6706,46 @@
       <c r="H165" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>180.250.219.58:53281</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1318.51</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:31:30</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:31:30</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12994,6 +13034,46 @@
       <c r="H165" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>180.250.219.58:53281</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1318.51</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:31:30</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:31:30</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -16045,21 +16125,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T11:46:50.925706</t>
+          <t>2026-03-28T14:31:30.012447</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2864864864864865</v>
+        <v>0.2903225806451613</v>
       </c>
     </row>
     <row r="4">
@@ -16253,7 +16333,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -16263,7 +16343,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
@@ -16323,7 +16403,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -16334,7 +16414,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T14:06:59</t>
+          <t>2026-03-28T14:31:30</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6746,6 +6746,158 @@
       <c r="H166" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>177.234.217.88:999</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>482.1</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>84.32.6.251:49146</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="n">
+        <v>2907.42</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>103.30.31.202:20326</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="n">
+        <v>2162.41</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>64.227.76.27:1080</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>833.2</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13074,6 +13226,158 @@
       <c r="H166" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>177.234.217.88:999</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>482.1</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>84.32.6.251:49146</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="n">
+        <v>2907.42</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>103.30.31.202:20326</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="n">
+        <v>2162.41</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>64.227.76.27:1080</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>833.2</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -13280,7 +13584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15220,6 +15524,86 @@
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>177.234.217.88:999</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>482.1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>64.227.76.27:1080</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>833.2</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:35:01</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -16098,21 +16482,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-28T14:06:59.478933</t>
+          <t>2026-03-28T14:35:01.519411</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3779904306220095</v>
+        <v>0.3867924528301887</v>
       </c>
     </row>
     <row r="3">
@@ -16125,21 +16509,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T14:31:30.012447</t>
+          <t>2026-03-28T14:35:01.512197</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="4">
@@ -16333,7 +16717,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3">
@@ -16343,7 +16727,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -16363,7 +16747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -16403,7 +16787,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -16414,7 +16798,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T14:31:30</t>
+          <t>2026-03-28T14:35:01</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6898,6 +6898,162 @@
       <c r="H170" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>194.59.204.87:9080</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>808.4400000000001</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>38.145.208.185:8444</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="n">
+        <v>1944.33</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>38.34.179.69:8453</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>955.63</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>38.145.208.229:8450</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>535.62</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -6912,7 +7068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13378,6 +13534,162 @@
       <c r="H170" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>194.59.204.87:9080</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>808.4400000000001</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>38.145.208.185:8444</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="n">
+        <v>1944.33</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>38.34.179.69:8453</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>955.63</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>38.145.208.229:8450</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>535.62</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15606,6 +15918,86 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>194.59.204.87:9080</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>808.4400000000001</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>38.34.179.69:8453</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>955.63</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -15620,7 +16012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16416,6 +16808,46 @@
         </is>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>38.145.208.229:8450</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>535.62</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:50:45</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -16509,21 +16941,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-28T14:35:01.512197</t>
+          <t>2026-03-28T14:50:45.434937</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3089005235602094</v>
       </c>
     </row>
     <row r="4">
@@ -16717,7 +17149,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -16727,7 +17159,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
@@ -16737,7 +17169,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -16747,7 +17179,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -16757,7 +17189,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -16787,7 +17219,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -16798,7 +17230,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T14:35:01</t>
+          <t>2026-03-28T14:50:45</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1318.51</v>
+        <v>1220.62</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 15:04:44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1318.51</v>
+        <v>1220.62</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 15:04:44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-28T14:58:49</t>
+          <t>2026-03-28T15:04:44</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -13,8 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Российские" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Американские" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Глобальные" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статистика" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статистика" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -958,7 +957,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1114,7 +1113,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1418,7 +1417,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1458,7 +1457,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1498,7 +1497,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1547,7 +1546,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>482.1</v>
+        <v>419.59</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1556,7 +1555,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1568,7 +1567,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>84.32.6.251:49146</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1578,12 +1577,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>2907.42</v>
+        <v>1050.46</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1592,7 +1595,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1604,7 +1607,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>103.30.31.202:20326</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1614,33 +1617,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>2162.41</v>
+        <v>808.4400000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.185:8444</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1650,37 +1657,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>833.2</v>
+        <v>1944.33</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>38.34.179.69:8453</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1695,11 +1698,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>808.4400000000001</v>
+        <v>955.63</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1720,7 +1723,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>38.145.208.185:8444</t>
+          <t>38.145.208.229:8450</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1730,12 +1733,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>1944.33</v>
+        <v>535.62</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1756,7 +1763,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>103.113.70.189:1081</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1775,28 +1782,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>955.63</v>
+        <v>313.29</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>38.145.208.229:8450</t>
+          <t>200.69.83.203:999</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1806,30 +1813,358 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>2196.32</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>190.97.243.27:999</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>2846.32</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1081</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>🌍 Глобальный</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>535.62</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>452.31</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>221.202.27.194:10810</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1206.72</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8123</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>222.184.48.242:22222</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>2315.93</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>185.76.240.44:10001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1547.7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>183.249.5.117:22222</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>2622.59</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8.213.151.128:3128</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>1043.76</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>566.91</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -1844,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2054,7 +2389,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2370,7 +2705,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2526,7 +2861,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2830,7 +3165,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2870,7 +3205,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2910,7 +3245,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2959,7 +3294,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>482.1</v>
+        <v>419.59</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2968,7 +3303,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2980,7 +3315,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>84.32.6.251:49146</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2990,12 +3325,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>2907.42</v>
+        <v>1050.46</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3004,7 +3343,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3016,7 +3355,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>103.30.31.202:20326</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3026,33 +3365,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>2162.41</v>
+        <v>808.4400000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.185:8444</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3062,37 +3405,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>833.2</v>
+        <v>1944.33</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>38.34.179.69:8453</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3107,11 +3446,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>808.4400000000001</v>
+        <v>955.63</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3132,7 +3471,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>38.145.208.185:8444</t>
+          <t>38.145.208.229:8450</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3142,12 +3481,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>1944.33</v>
+        <v>535.62</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3168,7 +3511,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>103.113.70.189:1081</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3187,28 +3530,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>955.63</v>
+        <v>313.29</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>38.145.208.229:8450</t>
+          <t>200.69.83.203:999</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3218,30 +3561,358 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>2196.32</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>190.97.243.27:999</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>2846.32</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1081</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>🌍 Глобальный</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>535.62</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>452.31</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>221.202.27.194:10810</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1206.72</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8123</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>222.184.48.242:22222</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>2315.93</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>185.76.240.44:10001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1547.7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>183.249.5.117:22222</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>2622.59</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8.213.151.128:3128</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>1043.76</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>566.91</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -3875,7 +4546,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>482.1</v>
+        <v>419.59</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3884,7 +4555,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3896,7 +4567,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3911,32 +4582,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>833.2</v>
+        <v>808.4400000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>38.34.179.69:8453</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3951,11 +4622,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>808.4400000000001</v>
+        <v>955.63</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3976,7 +4647,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>103.113.70.189:1081</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3995,21 +4666,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>955.63</v>
+        <v>313.29</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4186,6 +4857,86 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1081</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>452.31</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:21:23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>566.91</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -4200,369 +4951,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>источник</t>
+          <t>Показатель</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>активен</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>всего_найдено</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>рабочих_сейчас</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>последнее_появление</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>checks</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>success_rate</t>
+          <t>Значение</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-03-28T14:50:45.434937</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>191</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.3089005235602094</v>
+          <t>Всего прокси в базе</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
-        </is>
-      </c>
-      <c r="B3" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-03-28T14:58:49.954001</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Рабочих прокси</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-      <c r="B4" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-03-28T14:35:01.519411</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.3867924528301887</v>
+          <t>Российских</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
-        </is>
-      </c>
-      <c r="B5" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-03-28T14:58:49.960755</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>134</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.03731343283582089</v>
+          <t>Американских</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>thespeedx_socks4</t>
-        </is>
-      </c>
-      <c r="B6" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>130</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.007692307692307693</v>
+          <t>Глобальных</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jetkai_http</t>
-        </is>
-      </c>
-      <c r="B7" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-03-26T17:17:20.287448</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>130</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1801</v>
+          <t>Всего проверено за всё время</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>398</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ru_scrape</t>
-        </is>
-      </c>
-      <c r="B8" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-03-26T17:17:20.702123</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>130</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15.06153846153846</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>us_scrape</t>
-        </is>
-      </c>
-      <c r="B9" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-03-26T17:17:20.924234</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>130</v>
-      </c>
-      <c r="G9" t="n">
-        <v>97.72307692307692</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Всего прокси в базе</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Рабочих прокси</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Российских</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Американских</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Глобальных</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Активных источников</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Всего найдено источников</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Всего проверено за всё время</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
           <t>Последнее обновление</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-28T15:04:44</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-28T15:28:28</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2163,6 +2163,158 @@
         </is>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>113.11.97.193:30226</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1211.5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45.136.131.41:8451</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>2205.66</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5.104.87.17:8051</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>❓ JP</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1879.61</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2179,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3911,6 +4063,158 @@
         </is>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>113.11.97.193:30226</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1211.5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45.136.131.41:8451</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>2205.66</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5.104.87.17:8051</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>❓ JP</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1879.61</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4695,7 +4999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4935,6 +5239,46 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:41:05</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4973,7 +5317,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -4983,7 +5327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -5013,7 +5357,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -5023,7 +5367,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8">
@@ -5034,7 +5378,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T15:28:28</t>
+          <t>2026-03-28T15:41:05</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,6 +2315,126 @@
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>193.233.22.29:10808</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>388.27</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>200.174.198.32:8888</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1721.95</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>217.76.245.80:999</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>450.57</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2331,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4215,6 +4335,126 @@
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>193.233.22.29:10808</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>388.27</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>200.174.198.32:8888</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1721.95</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>217.76.245.80:999</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>450.57</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4343,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4983,6 +5223,46 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>217.76.245.80:999</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>450.57</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -4999,7 +5279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5279,6 +5559,46 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>193.233.22.29:10808</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>388.27</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:52:24</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5317,7 +5637,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -5327,7 +5647,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -5347,7 +5667,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -5357,7 +5677,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -5367,7 +5687,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
@@ -5378,7 +5698,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T15:41:05</t>
+          <t>2026-03-28T15:52:24</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>103.113.70.189:1081</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,32 +530,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>352.66</v>
+        <v>313.29</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:12:51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -570,15 +570,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>693.47</v>
+        <v>352.66</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,33 +605,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>1254.85</v>
+        <v>388.27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -641,37 +645,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ PH</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1214.32</v>
+        <v>419.59</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,33 +685,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>583.13</v>
+        <v>450.57</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>45.140.147.155:1081</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -717,37 +725,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1117.18</v>
+        <v>452.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -757,37 +765,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1256.07</v>
+        <v>525.63</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -797,20 +805,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>981.92</v>
+        <v>535.27</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -820,14 +828,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>38.145.208.229:8450</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -837,7 +845,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -846,28 +854,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1018.21</v>
+        <v>535.62</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,37 +885,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1345.62</v>
+        <v>554.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,25 +925,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>941.48</v>
+        <v>566.91</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -947,7 +955,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -957,20 +965,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>1795.91</v>
+        <v>583.13</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -980,14 +984,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -997,16 +1001,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>1068.87</v>
+        <v>674.05</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1023,7 +1031,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1033,20 +1041,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>535.27</v>
+        <v>693.47</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1056,14 +1064,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1078,20 +1086,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1092.02</v>
+        <v>808.4400000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1103,7 +1111,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1113,20 +1121,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1146.17</v>
+        <v>842.03</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1143,7 +1151,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1158,15 +1166,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>842.03</v>
+        <v>941.48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1183,7 +1191,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>38.34.179.69:8453</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1193,33 +1201,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>2004.52</v>
+        <v>955.63</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>158.160.215.167:8124</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1229,16 +1241,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>2879.83</v>
+        <v>981.92</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27 08:36:11</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1248,14 +1264,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1265,20 +1281,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>1242.56</v>
+        <v>985.21</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1295,7 +1307,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1305,16 +1317,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>985.21</v>
+        <v>1018.21</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1324,14 +1340,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>8.213.151.128:3128</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1341,37 +1357,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>674.05</v>
+        <v>1043.76</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,33 +1393,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>1748.35</v>
+        <v>1050.46</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1417,20 +1433,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>1200.56</v>
+        <v>1068.87</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1447,7 +1459,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1457,25 +1469,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>1899.77</v>
+        <v>1089.35</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1487,7 +1495,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1497,25 +1505,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1220.62</v>
+        <v>1092.02</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 15:04:44</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1527,7 +1535,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1542,32 +1550,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>419.59</v>
+        <v>1117.18</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1577,25 +1585,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1050.46</v>
+        <v>1146.17</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1607,7 +1615,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1617,25 +1625,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>808.4400000000001</v>
+        <v>1179.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1647,7 +1651,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>38.145.208.185:8444</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1657,21 +1661,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E32" t="n">
-        <v>1944.33</v>
+        <v>1200.56</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1683,7 +1691,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>221.202.27.194:10810</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1693,37 +1701,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>955.63</v>
+        <v>1206.72</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>38.145.208.229:8450</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1733,25 +1737,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>535.62</v>
+        <v>1211.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>103.113.70.189:1081</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1773,37 +1773,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>313.29</v>
+        <v>1214.32</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>200.69.83.203:999</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1813,33 +1813,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>2196.32</v>
+        <v>1220.62</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 15:04:44</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>190.97.243.27:999</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1849,33 +1853,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>2846.32</v>
+        <v>1242.56</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>45.140.147.155:1081</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1885,37 +1893,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>452.31</v>
+        <v>1254.85</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>221.202.27.194:10810</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1925,33 +1929,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>1206.72</v>
+        <v>1256.07</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1961,21 +1969,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>1179.6</v>
+        <v>1345.62</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1987,7 +1999,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>222.184.48.242:22222</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1997,26 +2009,30 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E41" t="n">
-        <v>2315.93</v>
+        <v>1521.71</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2075,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2069,21 +2085,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="E43" t="n">
-        <v>2622.59</v>
+        <v>1721.95</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2095,7 +2115,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8.213.151.128:3128</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2110,28 +2130,28 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1043.76</v>
+        <v>1748.35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2141,37 +2161,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>566.91</v>
+        <v>1795.91</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2181,12 +2201,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>❓ JP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>1211.5</v>
+        <v>1879.61</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2200,14 +2224,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>45.136.131.41:8451</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2217,21 +2241,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>2205.66</v>
+        <v>1899.77</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2243,7 +2271,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>38.145.208.185:8444</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2253,37 +2281,33 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ JP</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>1879.61</v>
+        <v>1944.33</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>45.140.147.82:1081</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2293,25 +2317,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>554.2</v>
+        <v>2004.52</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2323,7 +2343,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>200.69.83.203:999</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2333,25 +2353,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>388.27</v>
+        <v>2196.32</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2363,7 +2379,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>45.136.131.41:8451</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2373,37 +2389,33 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>1721.95</v>
+        <v>2205.66</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>222.184.48.242:22222</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2413,30 +2425,174 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>2315.93</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>183.249.5.117:22222</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>2622.59</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>190.97.243.27:999</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>2846.32</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8124</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>2879.83</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:58:49</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>450.57</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4457,6 +4613,162 @@
       <c r="H52" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>120.92.211.211:7890</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1089.35</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1082</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>525.63</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>38.34.179.192:8451</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1521.71</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5265,6 +5577,86 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>38.34.179.192:8451</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1521.71</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5599,6 +5991,46 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1082</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>525.63</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5637,7 +6069,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -5647,7 +6079,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -5667,7 +6099,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -5677,7 +6109,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -5687,7 +6119,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8">
@@ -5698,7 +6130,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T15:52:24</t>
+          <t>2026-03-28T16:03:06</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,7 +1071,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1086,20 +1086,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>808.4400000000001</v>
+        <v>706.86</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>842.03</v>
+        <v>808.4400000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1166,15 +1166,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>941.48</v>
+        <v>842.03</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1191,7 +1191,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1206,32 +1206,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>955.63</v>
+        <v>941.48</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>38.34.179.69:8453</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1246,32 +1246,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>981.92</v>
+        <v>955.63</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1281,16 +1281,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>985.21</v>
+        <v>981.92</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1300,14 +1304,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1317,20 +1321,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1018.21</v>
+        <v>985.21</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1340,14 +1340,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8.213.151.128:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1357,33 +1357,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E24" t="n">
-        <v>1043.76</v>
+        <v>1018.21</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>8.213.151.128:3128</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1393,25 +1397,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ NL</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1050.46</v>
+        <v>1043.76</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1438,28 +1438,28 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>1068.87</v>
+        <v>1048.39</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1469,33 +1469,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>1089.35</v>
+        <v>1050.46</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:08:23</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1505,20 +1509,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>1092.02</v>
+        <v>1068.87</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1545,37 +1545,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>1117.18</v>
+        <v>1089.35</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1585,7 +1581,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1594,11 +1590,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1146.17</v>
+        <v>1092.02</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1608,14 +1604,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1625,33 +1621,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>1179.6</v>
+        <v>1117.18</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1661,20 +1661,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1200.56</v>
+        <v>1146.17</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1684,14 +1684,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>221.202.27.194:10810</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1706,28 +1706,28 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1206.72</v>
+        <v>1179.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1737,21 +1737,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>1211.5</v>
+        <v>1200.56</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1763,7 +1767,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>221.202.27.194:10810</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1773,37 +1777,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>1214.32</v>
+        <v>1206.72</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1813,25 +1813,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>1220.62</v>
+        <v>1211.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:04:44</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1843,7 +1839,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1853,20 +1849,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1242.56</v>
+        <v>1214.32</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1876,14 +1872,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1893,33 +1889,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>1254.85</v>
+        <v>1220.62</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:04:44</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1934,15 +1934,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1256.07</v>
+        <v>1242.56</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1952,14 +1952,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1969,20 +1969,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1345.62</v>
+        <v>1254.85</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1992,14 +1988,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2014,32 +2010,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1521.71</v>
+        <v>1256.07</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2049,33 +2045,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E42" t="n">
-        <v>1547.7</v>
+        <v>1345.62</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2085,37 +2085,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>❓ BR</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1721.95</v>
+        <v>1521.71</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2130,16 +2130,16 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1748.35</v>
+        <v>1541.47</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2161,37 +2161,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1795.91</v>
+        <v>1547.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2201,25 +2197,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ JP</t>
+          <t>❓ BR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1879.61</v>
+        <v>1721.95</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2231,7 +2227,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2241,20 +2237,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>1899.77</v>
+        <v>1748.35</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2271,7 +2263,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>38.145.208.185:8444</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2281,33 +2273,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>❓ CN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
       <c r="E48" t="n">
-        <v>1944.33</v>
+        <v>1795.91</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2317,21 +2313,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>❓ JP</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
       <c r="E49" t="n">
-        <v>2004.52</v>
+        <v>1879.61</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>200.69.83.203:999</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2353,33 +2353,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E50" t="n">
-        <v>2196.32</v>
+        <v>1899.77</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>45.136.131.41:8451</t>
+          <t>38.145.208.185:8444</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2394,16 +2398,16 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2205.66</v>
+        <v>1944.33</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2415,7 +2419,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>222.184.48.242:22222</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2430,16 +2434,16 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>2315.93</v>
+        <v>2004.52</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2451,7 +2455,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>200.69.83.203:999</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2466,16 +2470,16 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2622.59</v>
+        <v>2196.32</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2487,7 +2491,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>190.97.243.27:999</t>
+          <t>45.136.131.41:8451</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2502,28 +2506,28 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2846.32</v>
+        <v>2205.66</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>158.160.215.167:8124</t>
+          <t>222.184.48.242:22222</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2538,61 +2542,205 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2879.83</v>
+        <v>2315.93</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-27 08:36:11</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>183.249.5.117:22222</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>2622.59</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:28:28</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>190.97.243.27:999</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>2846.32</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-03-28 15:19:05</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>158.160.215.167:8124</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>2879.83</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:58:49</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>38.145.220.13:8444</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E59" t="n">
         <v>2909.32</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>2026-03-28 16:03:06</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2026-03-28 16:03:06</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2926.76</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4769,6 +4917,154 @@
       <c r="H56" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>120.92.212.16:8890</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>1541.47</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>38.145.208.191:8445</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>706.86</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>150.107.140.238:3128</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>1048.39</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2926.76</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -4895,7 +5191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5655,6 +5951,46 @@
         </is>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>38.145.208.191:8445</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>706.86</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -6069,7 +6405,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -6079,7 +6415,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -6099,7 +6435,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -6119,7 +6455,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8">
@@ -6130,7 +6466,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:03:06</t>
+          <t>2026-03-28T16:06:43</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1691,7 +1691,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1706,28 +1706,28 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1179.6</v>
+        <v>1160.56</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1737,25 +1737,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1200.56</v>
+        <v>1179.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1767,7 +1763,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>221.202.27.194:10810</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1777,33 +1773,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>1206.72</v>
+        <v>1200.56</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>221.202.27.194:10810</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1818,28 +1818,28 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>1211.5</v>
+        <v>1206.72</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:21:23</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1849,37 +1849,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1214.32</v>
+        <v>1211.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1889,37 +1885,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1220.62</v>
+        <v>1214.32</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:04:44</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1929,25 +1925,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1242.56</v>
+        <v>1220.62</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:04:44</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1959,7 +1955,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1969,16 +1965,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>1254.85</v>
+        <v>1242.56</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1988,14 +1988,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2005,20 +2005,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1256.07</v>
+        <v>1254.85</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2035,7 +2031,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2050,15 +2046,15 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1345.62</v>
+        <v>1256.07</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2068,14 +2064,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2090,20 +2086,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1521.71</v>
+        <v>1345.62</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2115,7 +2111,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2125,21 +2121,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E44" t="n">
-        <v>1541.47</v>
+        <v>1521.71</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2166,28 +2166,28 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1547.7</v>
+        <v>1541.47</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2197,25 +2197,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1721.95</v>
+        <v>1547.7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2227,7 +2223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2237,33 +2233,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>1748.35</v>
+        <v>1721.95</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2273,20 +2273,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>1795.91</v>
+        <v>1748.35</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2296,14 +2292,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2313,37 +2309,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>❓ JP</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1879.61</v>
+        <v>1795.91</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2353,37 +2349,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>❓ JP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1899.77</v>
+        <v>1879.61</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>38.145.208.185:8444</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2393,21 +2389,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E51" t="n">
-        <v>1944.33</v>
+        <v>1899.77</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>38.145.208.185:8444</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2434,28 +2434,28 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>2004.52</v>
+        <v>1944.33</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>200.69.83.203:999</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2470,16 +2470,16 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2196.32</v>
+        <v>2004.52</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 14:58:49</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>45.136.131.41:8451</t>
+          <t>200.69.83.203:999</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2506,28 +2506,28 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2205.66</v>
+        <v>2196.32</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>222.184.48.242:22222</t>
+          <t>45.136.131.41:8451</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2542,28 +2542,28 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2315.93</v>
+        <v>2205.66</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>222.184.48.242:22222</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>2622.59</v>
+        <v>2315.93</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>190.97.243.27:999</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2614,16 +2614,16 @@
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2846.32</v>
+        <v>2573.29</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>158.160.215.167:8124</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2650,28 +2650,28 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>2879.83</v>
+        <v>2622.59</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-27 08:36:11</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>190.97.243.27:999</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2681,37 +2681,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>2909.32</v>
+        <v>2846.32</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:19:05</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>158.160.215.167:8124</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2726,19 +2722,95 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
+        <v>2879.83</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:36:11</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-28 14:58:49</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2755,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5063,6 +5135,78 @@
         </is>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>190.97.236.155:999</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>2573.29</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:11:47</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:11:47</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>103.156.15.210:1111</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>1160.56</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:11:47</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:11:47</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6405,7 +6549,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -6415,7 +6559,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -6455,7 +6599,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
@@ -6466,7 +6610,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:06:43</t>
+          <t>2026-03-28T16:11:47</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,33 +489,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>312.39</v>
+        <v>285.85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>103.113.70.189:1081</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,20 +534,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>313.29</v>
+        <v>293.97</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -555,7 +559,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,25 +569,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>352.66</v>
+        <v>388.57</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,37 +605,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>388.27</v>
+        <v>388.62</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,37 +645,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>419.59</v>
+        <v>421.33</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,25 +681,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>450.57</v>
+        <v>525.63</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -715,7 +711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>45.140.147.155:1081</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,37 +721,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>452.31</v>
+        <v>566.16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -774,16 +770,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>525.63</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -795,7 +791,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -805,37 +801,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535.27</v>
+        <v>706.86</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38.145.208.229:8450</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -845,37 +841,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>535.62</v>
+        <v>722.25</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>45.140.147.82:1081</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -885,37 +881,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>554.2</v>
+        <v>767.73</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -925,37 +917,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>566.91</v>
+        <v>813.27</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -965,33 +957,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>583.13</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1001,37 +997,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>674.05</v>
+        <v>847.64</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1041,37 +1037,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>693.47</v>
+        <v>856.22</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1086,20 +1082,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>706.86</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1111,7 +1107,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1126,32 +1122,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>808.4400000000001</v>
+        <v>970</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1161,37 +1157,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>842.03</v>
+        <v>992.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1201,25 +1197,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>941.48</v>
+        <v>1048.39</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1231,7 +1223,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1241,25 +1233,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>955.63</v>
+        <v>1068.15</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1271,7 +1259,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1281,37 +1269,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>981.92</v>
+        <v>1079.17</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1321,33 +1309,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>❓ CN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>985.21</v>
+        <v>1087.57</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1357,25 +1349,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1018.21</v>
+        <v>1087.62</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1387,7 +1375,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8.213.151.128:3128</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1402,28 +1390,28 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1043.76</v>
+        <v>1089.35</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1433,33 +1421,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>1048.39</v>
+        <v>1127.98</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1469,25 +1461,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ NL</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>1050.46</v>
+        <v>1160.56</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1499,7 +1487,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1509,33 +1497,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>❓ VN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>1068.87</v>
+        <v>1180.95</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1545,21 +1537,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E29" t="n">
-        <v>1089.35</v>
+        <v>1220.39</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1571,7 +1567,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1581,25 +1577,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1092.02</v>
+        <v>1221.44</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1611,7 +1607,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1621,37 +1617,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1117.18</v>
+        <v>1318.04</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1661,37 +1657,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1146.17</v>
+        <v>1350.83</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1701,33 +1697,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>1160.56</v>
+        <v>1521.71</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1742,16 +1742,16 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1179.6</v>
+        <v>1541.47</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1773,25 +1773,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>1200.56</v>
+        <v>1905.25</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1803,7 +1799,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>221.202.27.194:10810</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1818,28 +1814,28 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>1206.72</v>
+        <v>1907.03</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1854,28 +1850,28 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1211.5</v>
+        <v>1949.35</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1885,37 +1881,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ PH</t>
+          <t>❓ GB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1214.32</v>
+        <v>1963.18</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1925,25 +1921,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1220.62</v>
+        <v>2106.89</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:04:44</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1974,7 +1966,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1242.56</v>
+        <v>2108.46</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1983,7 +1975,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1995,7 +1987,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2010,28 +2002,28 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1254.85</v>
+        <v>2236.82</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2041,37 +2033,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1256.07</v>
+        <v>2332.34</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2086,32 +2074,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1345.62</v>
+        <v>2428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2121,37 +2109,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1521.71</v>
+        <v>2573.29</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2161,21 +2145,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>1541.47</v>
+        <v>2909.32</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2187,7 +2175,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>38.188.247.12:999</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2202,615 +2190,19 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1547.7</v>
+        <v>2926.76</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>200.174.198.32:8888</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1721.95</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>101.251.204.174:8080</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="n">
-        <v>1748.35</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-03-28 05:14:59</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:58:49</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>120.92.212.16:7890</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1795.91</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-26 17:05:06</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:58:49</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>thespeedx_socks5</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>5.104.87.17:8051</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>❓ JP</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>1879.61</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>128.199.254.13:9090</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1899.77</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-28 11:46:50</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:58:49</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>38.145.208.185:8444</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
-        <v>1944.33</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>16.78.119.130:443</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="n">
-        <v>2004.52</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-27 03:25:45</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:58:49</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>200.69.83.203:999</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="n">
-        <v>2196.32</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:19:05</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:19:05</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>45.136.131.41:8451</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="n">
-        <v>2205.66</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>222.184.48.242:22222</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
-        <v>2315.93</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>190.97.236.155:999</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="n">
-        <v>2573.29</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:11:47</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:11:47</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>183.249.5.117:22222</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
-        <v>2622.59</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>190.97.243.27:999</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="n">
-        <v>2846.32</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:19:05</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:19:05</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>158.160.215.167:8124</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
-        <v>2879.83</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-27 08:36:11</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:58:49</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>38.145.220.13:8444</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>2909.32</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>38.188.247.12:999</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
-        <v>2926.76</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2827,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2890,7 +2282,7 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>312.39</v>
+        <v>421.33</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2899,7 +2291,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2930,7 +2322,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>352.66</v>
+        <v>388.62</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2939,7 +2331,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2970,7 +2362,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>693.47</v>
+        <v>566.16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2979,7 +2371,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3006,7 +2398,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>1254.85</v>
+        <v>1087.62</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3015,7 +2407,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3046,7 +2438,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1214.32</v>
+        <v>1350.83</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3055,7 +2447,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3082,7 +2474,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>583.13</v>
+        <v>388.57</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3091,7 +2483,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3122,7 +2514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1117.18</v>
+        <v>1127.98</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3131,7 +2523,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3153,7 +2545,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ VN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3162,7 +2554,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1256.07</v>
+        <v>1180.95</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3171,7 +2563,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3202,7 +2594,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>981.92</v>
+        <v>970</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3211,7 +2603,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3242,7 +2634,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1018.21</v>
+        <v>2428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3251,7 +2643,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3273,16 +2665,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>1345.62</v>
+        <v>2332.34</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3291,7 +2679,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3322,7 +2710,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>941.48</v>
+        <v>847.64</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3331,7 +2719,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3362,7 +2750,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1795.91</v>
+        <v>1087.57</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3371,7 +2759,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3398,7 +2786,7 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>1068.87</v>
+        <v>1905.25</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3407,7 +2795,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3438,7 +2826,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>535.27</v>
+        <v>856.22</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3447,7 +2835,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3469,7 +2857,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3478,7 +2866,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1092.02</v>
+        <v>992.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3487,7 +2875,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3509,7 +2897,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3518,7 +2906,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1146.17</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3527,7 +2915,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3558,7 +2946,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>842.03</v>
+        <v>722.25</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3567,7 +2955,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3589,12 +2977,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>2004.52</v>
+        <v>1079.17</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3603,7 +2995,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3615,7 +3007,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>158.160.215.167:8124</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3625,21 +3017,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>2879.83</v>
+        <v>2108.46</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27 08:36:11</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3651,7 +3047,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3661,25 +3057,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>1242.56</v>
+        <v>767.73</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3691,7 +3083,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3701,21 +3093,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>985.21</v>
+        <v>1220.39</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3727,7 +3123,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3737,25 +3133,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>674.05</v>
+        <v>1068.15</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3767,7 +3159,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3777,21 +3169,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>1748.35</v>
+        <v>1221.44</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3803,7 +3199,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3813,25 +3209,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>1200.56</v>
+        <v>2106.89</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3843,7 +3235,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3853,25 +3245,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1899.77</v>
+        <v>1318.04</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3883,7 +3275,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3893,25 +3285,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1220.62</v>
+        <v>813.27</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 15:04:44</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3923,7 +3315,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3933,16 +3325,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>419.59</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3951,19 +3343,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3973,37 +3365,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1050.46</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4013,25 +3405,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>808.4400000000001</v>
+        <v>1907.03</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4043,7 +3431,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>38.145.208.185:8444</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4058,28 +3446,28 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>1944.33</v>
+        <v>1949.35</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4089,37 +3477,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ GB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>955.63</v>
+        <v>1963.18</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>38.145.208.229:8450</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,25 +3517,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>535.62</v>
+        <v>2236.82</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4159,7 +3543,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>103.113.70.189:1081</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4169,7 +3553,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4178,16 +3562,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>313.29</v>
+        <v>285.85</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4199,7 +3583,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>200.69.83.203:999</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4209,21 +3593,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>2196.32</v>
+        <v>293.97</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4235,7 +3623,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>190.97.243.27:999</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4245,33 +3633,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>2846.32</v>
+        <v>2909.32</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:19:05</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>45.140.147.155:1081</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4281,25 +3673,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>452.31</v>
+        <v>1089.35</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4311,7 +3699,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>221.202.27.194:10810</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4321,21 +3709,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>1206.72</v>
+        <v>525.63</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:21:23</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4347,7 +3739,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4357,21 +3749,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>1179.6</v>
+        <v>1521.71</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4383,7 +3779,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>222.184.48.242:22222</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4398,28 +3794,28 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>2315.93</v>
+        <v>1541.47</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4429,33 +3825,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E42" t="n">
-        <v>1547.7</v>
+        <v>706.86</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4470,16 +3870,16 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>2622.59</v>
+        <v>1048.39</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4491,7 +3891,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8.213.151.128:3128</t>
+          <t>38.188.247.12:999</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4506,16 +3906,16 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1043.76</v>
+        <v>2926.76</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4527,7 +3927,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4537,25 +3937,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>566.91</v>
+        <v>2573.29</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4567,7 +3963,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,631 +3978,19 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1211.5</v>
+        <v>1160.56</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45.136.131.41:8451</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="n">
-        <v>2205.66</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>5.104.87.17:8051</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>❓ JP</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1879.61</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1081</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>554.2</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>193.233.22.29:10808</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>388.27</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>200.174.198.32:8888</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1721.95</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>217.76.245.80:999</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>450.57</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>38.145.220.13:8444</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>2909.32</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>120.92.211.211:7890</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="n">
-        <v>1089.35</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1082</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>525.63</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>38.34.179.192:8451</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1521.71</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>120.92.212.16:8890</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="n">
-        <v>1541.47</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>38.145.208.191:8445</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>706.86</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>150.107.140.238:3128</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="n">
-        <v>1048.39</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>38.188.247.12:999</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
-        <v>2926.76</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>190.97.236.155:999</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="n">
-        <v>2573.29</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:11:47</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:11:47</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>103.156.15.210:1111</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
-        <v>1160.56</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:11:47</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:11:47</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -5335,7 +4119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5402,7 +4186,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>352.66</v>
+        <v>388.62</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5411,7 +4195,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5442,7 +4226,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>693.47</v>
+        <v>566.16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5451,7 +4235,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5482,7 +4266,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1117.18</v>
+        <v>1127.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5491,7 +4275,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5503,7 +4287,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5518,20 +4302,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1256.07</v>
+        <v>970</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5543,7 +4327,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5558,20 +4342,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>981.92</v>
+        <v>2428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5583,7 +4367,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5598,32 +4382,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1018.21</v>
+        <v>847.64</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5638,32 +4422,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1345.62</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5678,20 +4462,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>941.48</v>
+        <v>722.25</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5703,7 +4487,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5718,20 +4502,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1092.02</v>
+        <v>2108.46</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5743,7 +4527,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5758,32 +4542,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>842.03</v>
+        <v>1220.39</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5798,20 +4582,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1242.56</v>
+        <v>813.27</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5823,7 +4607,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5838,20 +4622,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>419.59</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 15:08:23</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5863,7 +4647,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5878,32 +4662,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>808.4400000000001</v>
+        <v>293.97</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>38.34.179.69:8453</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5922,16 +4706,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>955.63</v>
+        <v>2909.32</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5943,7 +4727,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>103.113.70.189:1081</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5962,28 +4746,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>313.29</v>
+        <v>1521.71</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 15:12:51</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5998,143 +4782,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>450.57</v>
+        <v>706.86</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>38.145.220.13:8444</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2909.32</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>38.34.179.192:8451</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1521.71</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>38.145.208.191:8445</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>706.86</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -6151,7 +4815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6218,7 +4882,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>535.27</v>
+        <v>856.22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6227,7 +4891,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6239,7 +4903,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6258,28 +4922,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>674.05</v>
+        <v>285.85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 14:58:49</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>38.145.208.229:8450</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6294,223 +4958,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>535.62</v>
+        <v>525.63</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>45.140.147.155:1081</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>452.31</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:21:23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:21:23</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>86.53.183.16:1080</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>566.91</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1081</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>554.2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:41:05</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>193.233.22.29:10808</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>388.27</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1082</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>525.63</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -6549,7 +5013,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -6559,7 +5023,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -6579,7 +5043,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -6589,7 +5053,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6610,7 +5074,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:11:47</t>
+          <t>2026-03-28T16:26:45</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,20 +489,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>285.85</v>
+        <v>388.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,14 +508,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -534,15 +530,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>293.97</v>
+        <v>388.62</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,14 +548,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,11 +570,11 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>388.57</v>
+        <v>421.33</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -595,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,37 +601,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>388.62</v>
+        <v>513.33</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,33 +641,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>421.33</v>
+        <v>525.63</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,37 +681,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>525.63</v>
+        <v>566.16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,25 +726,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>566.16</v>
+        <v>573.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -841,20 +841,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>722.25</v>
+        <v>767.73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -864,14 +860,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -881,16 +877,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>767.73</v>
+        <v>813.27</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -922,15 +922,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>813.27</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -940,14 +940,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -962,15 +962,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>826.8200000000001</v>
+        <v>847.64</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -997,20 +997,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>847.64</v>
+        <v>856.22</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1037,37 +1037,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>856.22</v>
+        <v>924.5700000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1077,37 +1077,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>960.4400000000001</v>
+        <v>935.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1122,15 +1118,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>970</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1183,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1202,28 +1198,28 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>1048.39</v>
+        <v>1068.15</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1233,33 +1229,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>1068.15</v>
+        <v>1071.77</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1269,20 +1269,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1079.17</v>
+        <v>1087.57</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1292,14 +1292,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1309,20 +1309,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1087.57</v>
+        <v>1087.62</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1332,14 +1328,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1354,28 +1350,28 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1087.62</v>
+        <v>1089.35</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1385,33 +1381,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>1089.35</v>
+        <v>1127.98</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,37 +1421,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>1127.98</v>
+        <v>1160.56</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1461,33 +1457,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>1160.56</v>
+        <v>1205.42</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1180.95</v>
+        <v>1220.39</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1520,14 +1520,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1537,20 +1537,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1220.39</v>
+        <v>1221.44</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1577,20 +1577,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1221.44</v>
+        <v>1318.04</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1617,20 +1617,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1318.04</v>
+        <v>1350.83</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1657,37 +1657,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>1350.83</v>
+        <v>1450.08</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1697,37 +1693,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1521.71</v>
+        <v>1465.88</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1737,33 +1733,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>❓ VN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>1541.47</v>
+        <v>1502.59</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1773,21 +1773,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>1905.25</v>
+        <v>1521.71</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1799,7 +1803,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1814,16 +1818,16 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>1907.03</v>
+        <v>1541.47</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1835,7 +1839,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1850,11 +1854,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1949.35</v>
+        <v>1905.25</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1864,14 +1868,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1881,16 +1885,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ GB</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1963.18</v>
+        <v>1907.03</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1926,11 +1926,11 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>2106.89</v>
+        <v>1949.35</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1957,20 +1957,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ GB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2108.46</v>
+        <v>1963.18</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1980,14 +1980,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>2236.82</v>
+        <v>2106.89</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2023,7 +2023,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2033,16 +2033,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E42" t="n">
-        <v>2332.34</v>
+        <v>2108.46</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2059,7 +2063,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2069,20 +2073,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>2428</v>
+        <v>2236.82</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2109,33 +2109,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E44" t="n">
-        <v>2573.29</v>
+        <v>2428</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2145,37 +2149,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ BR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2909.32</v>
+        <v>2430.36</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2190,19 +2194,167 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
+        <v>2573.29</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:11:47</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:11:47</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1.231.81.166:3128</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>2752.34</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-24 16:40:38</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2219,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2554,7 +2706,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1180.95</v>
+        <v>1502.59</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2563,12 +2715,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2746,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>970</v>
+        <v>1205.42</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2603,12 +2755,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2822,7 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>2332.34</v>
+        <v>2752.34</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2679,12 +2831,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2946,7 +3098,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>722.25</v>
+        <v>924.5700000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2955,12 +3107,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3129,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2986,7 +3138,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1079.17</v>
+        <v>1071.77</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2995,12 +3147,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3714,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>285.85</v>
+        <v>513.33</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3571,12 +3723,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3754,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>293.97</v>
+        <v>573.7</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3611,12 +3763,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3870,7 +4022,7 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1048.39</v>
+        <v>1450.08</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3879,12 +4031,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3993,6 +4145,158 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>148.222.152.4:999</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>935.3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>59.46.216.131:30001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>❓ CN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1465.88</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>200.174.198.32:8888</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2430.36</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4306,7 +4610,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>970</v>
+        <v>1205.42</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4315,12 +4619,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4770,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>722.25</v>
+        <v>924.5700000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4475,19 +4779,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4502,32 +4806,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2108.46</v>
+        <v>1071.77</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4546,11 +4850,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1220.39</v>
+        <v>2108.46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4567,7 +4871,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4582,15 +4886,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>813.27</v>
+        <v>1220.39</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4607,7 +4911,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4622,15 +4926,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>960.4400000000001</v>
+        <v>813.27</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4647,7 +4951,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4662,15 +4966,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>293.97</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4680,14 +4984,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4702,32 +5006,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2909.32</v>
+        <v>573.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4746,7 +5050,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1521.71</v>
+        <v>2909.32</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4767,38 +5071,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>38.34.179.192:8451</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1521.71</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>38.145.208.191:8445</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>706.86</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>proxymania</t>
         </is>
@@ -4922,7 +5266,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>285.85</v>
+        <v>513.33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4931,12 +5275,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5357,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -5023,7 +5367,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -5043,7 +5387,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -5063,7 +5407,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8">
@@ -5074,7 +5418,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:26:45</t>
+          <t>2026-03-28T16:34:22</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,7 +711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -721,37 +721,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>573.7</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,37 +761,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>676.4400000000001</v>
+        <v>706.86</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,25 +801,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>706.86</v>
+        <v>767.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -841,16 +837,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>767.73</v>
+        <v>813.27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -882,15 +882,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>813.27</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -900,14 +900,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -922,15 +922,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>826.8200000000001</v>
+        <v>847.64</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -957,20 +957,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>847.64</v>
+        <v>856.22</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -997,37 +997,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>856.22</v>
+        <v>935.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1042,32 +1038,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>924.5700000000001</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>148.222.152.4:999</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1082,28 +1078,28 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>935.3</v>
+        <v>1068.15</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1118,32 +1114,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>960.4400000000001</v>
+        <v>1071.77</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1153,20 +1149,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>992.1</v>
+        <v>1087.57</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1176,14 +1172,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1198,11 +1194,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>1068.15</v>
+        <v>1087.62</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1212,14 +1208,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1229,37 +1225,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>1071.77</v>
+        <v>1089.35</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1269,20 +1261,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>❓ CN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1087.57</v>
+        <v>1127.98</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1292,14 +1284,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1309,33 +1301,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>1087.62</v>
+        <v>1136.13</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1350,28 +1346,28 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1089.35</v>
+        <v>1160.56</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1386,15 +1382,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1127.98</v>
+        <v>1220.39</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1404,14 +1400,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,33 +1417,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>1160.56</v>
+        <v>1221.44</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1457,20 +1457,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>1205.42</v>
+        <v>1450.08</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1487,7 +1483,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1497,37 +1493,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ VN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1220.39</v>
+        <v>1502.59</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1537,25 +1533,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1221.44</v>
+        <v>1521.71</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1567,7 +1563,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1577,25 +1573,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>1318.04</v>
+        <v>1541.47</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1607,7 +1599,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1617,37 +1609,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ PH</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1350.83</v>
+        <v>1584.86</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1657,21 +1649,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E32" t="n">
-        <v>1450.08</v>
+        <v>1712.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1683,7 +1679,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1693,25 +1689,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>❓ CN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1465.88</v>
+        <v>1776.26</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1723,7 +1719,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1733,25 +1729,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ VN</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1502.59</v>
+        <v>1782.81</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1763,7 +1755,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1778,32 +1770,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1521.71</v>
+        <v>1825.89</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1813,26 +1805,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>1541.47</v>
+        <v>1895.98</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1943,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1957,30 +1953,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ GB</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1963.18</v>
+        <v>2052.95</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2055,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2078,28 +2070,28 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>2236.82</v>
+        <v>2197.44</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2109,20 +2101,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>2428</v>
+        <v>2236.82</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2132,14 +2120,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2149,16 +2137,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>2430.36</v>
+        <v>2245.34</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2167,7 +2151,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2179,7 +2163,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2189,33 +2173,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>❓ GB</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>2573.29</v>
+        <v>2413.23</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2225,33 +2213,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>2752.34</v>
+        <v>2428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2261,37 +2253,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ BR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2909.32</v>
+        <v>2430.36</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2306,28 +2298,28 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2913.53</v>
+        <v>2573.29</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2337,24 +2329,172 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
+        <v>2729.47</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1.231.81.166:3128</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>2752.34</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-24 16:40:38</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2371,7 +2511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2581,16 +2721,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>1350.83</v>
+        <v>1782.81</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2599,12 +2735,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2882,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205.42</v>
+        <v>1776.26</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2755,7 +2891,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3009,7 +3145,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3018,7 +3154,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>992.1</v>
+        <v>1825.89</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3027,12 +3163,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3234,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>924.5700000000001</v>
+        <v>1584.86</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3107,7 +3243,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3406,7 +3542,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1318.04</v>
+        <v>1895.98</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3415,12 +3551,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3774,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1963.18</v>
+        <v>2413.23</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3647,12 +3783,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3890,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>573.7</v>
+        <v>1136.13</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3763,7 +3899,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4197,16 +4333,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>1465.88</v>
+        <v>2245.34</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4215,7 +4347,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4295,6 +4427,154 @@
         </is>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>103.30.30.5:20326</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>2729.47</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>45.15.158.60:2222</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1712.6</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>180.125.216.109:8118</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>2052.95</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>117.50.7.101:8000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>2197.44</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -4423,7 +4703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4610,7 +4890,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205.42</v>
+        <v>1776.26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4619,7 +4899,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4711,7 +4991,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4730,28 +5010,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>826.8200000000001</v>
+        <v>1825.89</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4766,32 +5046,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>924.5700000000001</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4806,20 +5086,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1071.77</v>
+        <v>1584.86</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4831,7 +5111,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4846,32 +5126,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2108.46</v>
+        <v>1071.77</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4890,11 +5170,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1220.39</v>
+        <v>2108.46</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4911,7 +5191,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4926,15 +5206,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>813.27</v>
+        <v>1220.39</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4951,7 +5231,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4966,15 +5246,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>960.4400000000001</v>
+        <v>813.27</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4991,7 +5271,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5006,32 +5286,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>573.7</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5046,32 +5326,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2909.32</v>
+        <v>1136.13</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5090,7 +5370,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1521.71</v>
+        <v>2909.32</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -5111,40 +5391,116 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>38.34.179.192:8451</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1521.71</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>38.145.208.191:8445</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>706.86</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>103.30.30.5:20326</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>2729.47</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5321,6 +5677,46 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>45.15.158.60:2222</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1712.6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5753,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -5367,7 +5763,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -5377,7 +5773,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -5387,7 +5783,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -5397,7 +5793,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -5407,7 +5803,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8">
@@ -5418,7 +5814,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:34:22</t>
+          <t>2026-03-28T16:44:58</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,16 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>388.62</v>
+        <v>421.33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -555,7 +551,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,33 +561,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>421.33</v>
+        <v>525.63</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,37 +601,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>513.33</v>
+        <v>566.16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>525.63</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,32 +686,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>566.16</v>
+        <v>706.86</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -721,20 +721,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>❓ NL</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>676.4400000000001</v>
+        <v>767.73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -744,14 +740,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -766,20 +762,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>706.86</v>
+        <v>813.27</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -791,7 +787,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,16 +797,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>767.73</v>
+        <v>856.22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -820,14 +820,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -837,37 +837,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>813.27</v>
+        <v>894.51</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,37 +877,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>826.8200000000001</v>
+        <v>935.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -922,15 +918,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>847.64</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -940,14 +936,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -962,32 +958,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>856.22</v>
+        <v>969.75</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>148.222.152.4:999</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1002,28 +998,28 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>935.3</v>
+        <v>1068.15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1033,20 +1029,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>960.4400000000001</v>
+        <v>1087.57</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1056,14 +1052,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1078,11 +1074,11 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1068.15</v>
+        <v>1087.62</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1092,14 +1088,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1109,37 +1105,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1071.77</v>
+        <v>1089.35</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>144.124.227.90:21074</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1149,37 +1141,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1087.57</v>
+        <v>1108.62</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1189,33 +1177,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>1087.62</v>
+        <v>1136.13</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1230,28 +1222,28 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>1089.35</v>
+        <v>1160.56</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1266,32 +1258,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1127.98</v>
+        <v>1213.81</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1306,32 +1298,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1136.13</v>
+        <v>1220.39</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1341,33 +1333,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E24" t="n">
-        <v>1160.56</v>
+        <v>1221.44</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1377,37 +1373,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1220.39</v>
+        <v>1450.08</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1417,37 +1409,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>❓ VN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1221.44</v>
+        <v>1502.59</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1457,33 +1449,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>1450.08</v>
+        <v>1521.71</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1493,37 +1489,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ VN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>1502.59</v>
+        <v>1541.47</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1538,32 +1530,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1521.71</v>
+        <v>1584.86</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1573,33 +1565,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>1541.47</v>
+        <v>1595.53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1614,20 +1610,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1584.86</v>
+        <v>1624.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1639,7 +1635,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1649,25 +1645,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>1712.6</v>
+        <v>1695.07</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1679,7 +1671,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1689,20 +1681,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1776.26</v>
+        <v>1712.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1719,7 +1711,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1729,16 +1721,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>1782.81</v>
+        <v>1776.26</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1755,7 +1751,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1765,20 +1761,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>1825.89</v>
+        <v>1782.81</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1795,7 +1787,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1805,25 +1797,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1895.98</v>
+        <v>1814.42</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1835,7 +1827,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1845,33 +1837,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>1905.25</v>
+        <v>1895.98</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1886,11 +1882,11 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1907.03</v>
+        <v>1905.25</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1907,7 +1903,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1922,7 +1918,7 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1949.35</v>
+        <v>1907.03</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1936,14 +1932,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>180.125.216.109:8118</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1958,28 +1954,28 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>2052.95</v>
+        <v>1949.35</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1994,28 +1990,28 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>2106.89</v>
+        <v>2052.95</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2025,20 +2021,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>2108.46</v>
+        <v>2106.89</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2055,7 +2047,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2065,33 +2057,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E43" t="n">
-        <v>2197.44</v>
+        <v>2108.46</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2106,28 +2102,28 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>2236.82</v>
+        <v>2197.44</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2142,28 +2138,28 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>2245.34</v>
+        <v>2236.82</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2173,20 +2169,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ GB</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>2413.23</v>
+        <v>2245.34</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2203,7 +2195,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2213,37 +2205,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ GB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2428</v>
+        <v>2413.23</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2253,37 +2245,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ BR</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2430.36</v>
+        <v>2428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2293,33 +2285,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="E49" t="n">
-        <v>2573.29</v>
+        <v>2430.36</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2332,18 +2328,22 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E50" t="n">
-        <v>2729.47</v>
+        <v>2539.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2355,7 +2355,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2370,28 +2370,28 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2752.34</v>
+        <v>2573.29</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2401,37 +2401,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2909.32</v>
+        <v>2715.84</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2441,21 +2441,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2913.53</v>
+        <v>2729.47</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2467,34 +2467,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>38.188.247.12:999</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>❓ Неизвестно</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="n">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2511,7 +2587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2605,7 +2681,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2614,7 +2690,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388.62</v>
+        <v>969.75</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2623,12 +2699,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2878,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1127.98</v>
+        <v>1624.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2811,12 +2887,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2953,12 +3029,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>2752.34</v>
+        <v>2539.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2967,7 +3047,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2998,7 +3078,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>847.64</v>
+        <v>1814.42</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3007,12 +3087,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3145,16 +3225,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1825.89</v>
+        <v>1695.07</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3163,7 +3239,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3185,7 +3261,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3194,7 +3270,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>826.8200000000001</v>
+        <v>2715.84</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3203,12 +3279,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3341,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3274,7 +3350,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1071.77</v>
+        <v>1595.53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3283,7 +3359,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3850,7 +3926,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>513.33</v>
+        <v>894.51</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3859,7 +3935,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4575,6 +4651,82 @@
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>186.148.180.46:999</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1213.81</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:49:31</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:49:31</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>144.124.227.90:21074</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>1108.62</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:49:31</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:49:31</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -4703,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4751,7 +4903,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4766,15 +4918,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>388.62</v>
+        <v>566.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4791,7 +4943,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4806,32 +4958,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>566.16</v>
+        <v>1624.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4850,28 +5002,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1127.98</v>
+        <v>1776.26</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4886,32 +5038,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1776.26</v>
+        <v>2428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4926,25 +5078,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2428</v>
+        <v>2539.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -4970,7 +5122,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>847.64</v>
+        <v>1814.42</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4979,19 +5131,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5006,15 +5158,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1825.89</v>
+        <v>1584.86</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5031,7 +5183,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5046,15 +5198,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>826.8200000000001</v>
+        <v>2108.46</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5064,14 +5216,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5086,32 +5238,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1584.86</v>
+        <v>1220.39</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5126,32 +5278,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1071.77</v>
+        <v>813.27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5166,15 +5318,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2108.46</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5191,7 +5343,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5206,32 +5358,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1220.39</v>
+        <v>1136.13</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5246,20 +5398,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>813.27</v>
+        <v>2909.32</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5271,7 +5423,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5286,20 +5438,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>960.4400000000001</v>
+        <v>1521.71</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5311,7 +5463,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5326,32 +5478,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1136.13</v>
+        <v>706.86</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5364,34 +5516,30 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2909.32</v>
+        <v>2729.47</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5406,99 +5554,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1521.71</v>
+        <v>1213.81</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>38.145.208.191:8445</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>706.86</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>proxymania</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>103.30.30.5:20326</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="n">
-        <v>2729.47</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5515,7 +5587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5563,7 +5635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5578,32 +5650,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>856.22</v>
+        <v>969.75</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5618,32 +5690,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>513.33</v>
+        <v>856.22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5658,63 +5730,103 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>525.63</v>
+        <v>894.51</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>45.140.147.82:1082</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>525.63</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>45.15.158.60:2222</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>🌍 Глобальный</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>RU</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>1712.6</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-03-28 16:44:58</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-03-28 16:44:58</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5753,7 +5865,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -5763,7 +5875,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -5773,7 +5885,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -5783,7 +5895,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -5793,7 +5905,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5803,7 +5915,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8">
@@ -5814,7 +5926,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:44:58</t>
+          <t>2026-03-28T16:49:31</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,33 +525,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>421.33</v>
+        <v>525.63</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,37 +565,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>525.63</v>
+        <v>566.16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,20 +605,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>566.16</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -624,14 +628,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -641,37 +645,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>676.4400000000001</v>
+        <v>706.86</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -681,25 +685,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>706.86</v>
+        <v>767.73</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -721,16 +721,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>767.73</v>
+        <v>813.27</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -747,7 +751,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -757,20 +761,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>813.27</v>
+        <v>856.22</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -780,14 +784,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -802,32 +806,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>856.22</v>
+        <v>894.51</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -837,25 +841,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>894.51</v>
+        <v>935.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>148.222.152.4:999</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,33 +877,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>935.3</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -913,37 +917,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>960.4400000000001</v>
+        <v>969.75</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -953,37 +957,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>969.75</v>
+        <v>1068.15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -993,16 +993,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>❓ CN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>1068.15</v>
+        <v>1087.57</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1012,14 +1016,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1029,37 +1033,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>1087.57</v>
+        <v>1089.35</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>144.124.227.90:21074</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1074,28 +1074,28 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1087.62</v>
+        <v>1108.62</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1105,33 +1105,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>1089.35</v>
+        <v>1136.13</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>144.124.227.90:21074</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1146,28 +1150,28 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1108.62</v>
+        <v>1160.56</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1182,20 +1186,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1136.13</v>
+        <v>1213.81</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1207,7 +1211,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1217,33 +1221,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>1160.56</v>
+        <v>1220.39</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1253,37 +1261,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1213.81</v>
+        <v>1221.44</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1293,37 +1301,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1220.39</v>
+        <v>1353.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1333,37 +1337,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>❓ SG</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1221.44</v>
+        <v>1450.08</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1373,16 +1373,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>❓ VN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>1450.08</v>
+        <v>1502.59</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1399,7 +1403,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1409,37 +1413,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1502.59</v>
+        <v>1521.71</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1449,25 +1453,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>1521.71</v>
+        <v>1541.47</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1489,33 +1489,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>1541.47</v>
+        <v>1584.86</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1525,25 +1529,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1584.86</v>
+        <v>1595.53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1555,7 +1559,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1565,20 +1569,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>1595.53</v>
+        <v>1695.07</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1605,25 +1605,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1624.5</v>
+        <v>1712.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1645,21 +1645,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E32" t="n">
-        <v>1695.07</v>
+        <v>1776.26</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1671,7 +1675,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1681,20 +1685,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1712.6</v>
+        <v>1782.81</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1776.26</v>
+        <v>1832.39</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1761,21 +1761,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>1782.81</v>
+        <v>1846.61</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1787,7 +1791,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1797,25 +1801,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1814.42</v>
+        <v>1895.98</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1827,7 +1831,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1837,37 +1841,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1895.98</v>
+        <v>1905.25</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1882,11 +1882,11 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1905.25</v>
+        <v>1907.03</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1903,7 +1903,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1907.03</v>
+        <v>1949.35</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1954,21 +1954,21 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1949.35</v>
+        <v>2035.82</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2138,28 +2138,28 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>2236.82</v>
+        <v>2220.89</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2174,28 +2174,28 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>2245.34</v>
+        <v>2236.82</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2205,20 +2205,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ GB</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2413.23</v>
+        <v>2245.34</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2235,7 +2231,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2245,37 +2241,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ GB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2428</v>
+        <v>2413.23</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2285,37 +2281,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>❓ BR</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2430.36</v>
+        <v>2428</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2325,25 +2321,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ BR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2539.7</v>
+        <v>2430.36</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2355,7 +2351,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2370,28 +2366,28 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2573.29</v>
+        <v>2438.16</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2401,20 +2397,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2715.84</v>
+        <v>2539.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2431,7 +2427,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2441,33 +2437,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2729.47</v>
+        <v>2573.29</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2477,37 +2473,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2909.32</v>
+        <v>2715.84</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2517,21 +2513,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2913.53</v>
+        <v>2729.47</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2543,7 +2539,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2558,19 +2554,131 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
+        <v>2894.14</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2587,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2650,7 +2758,7 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>421.33</v>
+        <v>1353.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2659,12 +2767,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2874,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>1087.62</v>
+        <v>2438.16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2775,12 +2883,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2986,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1624.5</v>
+        <v>1832.39</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2887,7 +2995,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3078,7 +3186,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1814.42</v>
+        <v>1846.61</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3087,7 +3195,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4727,6 +4835,114 @@
         </is>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>202.154.18.80:8082</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>2035.82</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>210.87.125.57:8080</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>2894.14</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>5.104.87.17:8051</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>2220.89</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:03:48</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -4962,7 +5178,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1624.5</v>
+        <v>1832.39</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4971,7 +5187,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5122,7 +5338,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1814.42</v>
+        <v>1846.61</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -5131,7 +5347,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5865,7 +6081,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -5875,7 +6091,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -5915,7 +6131,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8">
@@ -5926,7 +6142,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T16:49:31</t>
+          <t>2026-03-28T17:03:48</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,33 +489,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>388.57</v>
+        <v>525.63</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,37 +529,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>525.63</v>
+        <v>566.16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,20 +569,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>566.16</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,14 +592,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,37 +609,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>676.4400000000001</v>
+        <v>706.86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,25 +649,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>706.86</v>
+        <v>767.73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,16 +685,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>767.73</v>
+        <v>813.27</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -711,7 +715,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -721,20 +725,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>813.27</v>
+        <v>856.22</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -744,14 +748,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -766,32 +770,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>856.22</v>
+        <v>894.51</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,25 +805,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>894.51</v>
+        <v>935.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>148.222.152.4:999</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -841,33 +841,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>935.3</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,20 +881,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>960.4400000000001</v>
+        <v>1068.15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,37 +917,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>969.75</v>
+        <v>1087.57</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -962,16 +962,16 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>1068.15</v>
+        <v>1089.35</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>144.124.227.90:21074</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -993,37 +993,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>1087.57</v>
+        <v>1108.62</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1033,33 +1029,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>1089.35</v>
+        <v>1136.13</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>144.124.227.90:21074</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1074,28 +1074,28 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1108.62</v>
+        <v>1160.56</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1105,25 +1105,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1136.13</v>
+        <v>1161.27</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1135,7 +1131,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1150,21 +1146,21 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1160.56</v>
+        <v>1195.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1287,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1306,16 +1302,16 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1353.4</v>
+        <v>1450.08</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1327,7 +1323,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1337,16 +1333,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>❓ VN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E24" t="n">
-        <v>1450.08</v>
+        <v>1502.59</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1373,37 +1373,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1502.59</v>
+        <v>1521.71</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1418,25 +1418,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1521.71</v>
+        <v>1525.53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1494,20 +1494,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1584.86</v>
+        <v>1569</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1529,25 +1529,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1595.53</v>
+        <v>1608.13</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1569,21 +1569,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>1695.07</v>
+        <v>1611.29</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1595,7 +1599,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1605,25 +1609,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>1712.6</v>
+        <v>1675.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1776.26</v>
+        <v>1684.35</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1690,16 +1690,16 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1782.81</v>
+        <v>1695.07</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1721,25 +1721,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1832.39</v>
+        <v>1712.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1761,25 +1761,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>1846.61</v>
+        <v>1714.98</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1791,7 +1787,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1801,20 +1797,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>1895.98</v>
+        <v>1782.81</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1831,7 +1823,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1841,33 +1833,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1905.25</v>
+        <v>1793.03</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1877,33 +1869,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>1907.03</v>
+        <v>1895.98</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1918,11 +1914,11 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1949.35</v>
+        <v>1905.25</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1932,14 +1928,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1954,28 +1950,28 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>2035.82</v>
+        <v>1907.03</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>180.125.216.109:8118</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1990,16 +1986,16 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>2052.95</v>
+        <v>1935.13</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2011,7 +2007,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2026,11 +2022,11 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>2106.89</v>
+        <v>1949.35</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2040,14 +2036,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2057,37 +2053,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>2108.46</v>
+        <v>2035.82</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2102,7 +2094,7 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>2197.44</v>
+        <v>2052.95</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2123,7 +2115,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2133,21 +2125,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>2220.89</v>
+        <v>2060.77</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2159,7 +2155,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2174,11 +2170,11 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>2236.82</v>
+        <v>2106.89</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2195,7 +2191,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2205,33 +2201,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>2245.34</v>
+        <v>2108.46</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2241,20 +2241,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ GB</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2413.23</v>
+        <v>2197.44</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2271,7 +2267,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2281,37 +2277,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2428</v>
+        <v>2220.89</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2321,37 +2313,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>2430.36</v>
+        <v>2236.82</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2366,16 +2354,16 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2438.16</v>
+        <v>2245.34</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2387,7 +2375,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2402,32 +2390,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2539.7</v>
+        <v>2428</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2437,33 +2425,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="E53" t="n">
-        <v>2573.29</v>
+        <v>2430.36</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2473,25 +2465,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>❓ HK</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2715.84</v>
+        <v>2438.16</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2503,7 +2491,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2516,18 +2504,22 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E55" t="n">
-        <v>2729.47</v>
+        <v>2539.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2539,7 +2531,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2554,28 +2546,28 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>2894.14</v>
+        <v>2573.29</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2585,37 +2577,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2909.32</v>
+        <v>2715.84</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2625,21 +2617,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>2913.53</v>
+        <v>2729.47</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2651,34 +2643,110 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>38.188.247.12:999</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>❓ Неизвестно</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="n">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2695,7 +2763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2758,7 +2826,7 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>1353.4</v>
+        <v>1161.27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2767,7 +2835,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2789,16 +2857,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>969.75</v>
+        <v>1793.03</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2807,7 +2871,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2946,7 +3010,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>388.57</v>
+        <v>1195.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2955,12 +3019,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2986,7 +3050,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1832.39</v>
+        <v>1608.13</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2995,7 +3059,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3066,7 +3130,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1776.26</v>
+        <v>1684.35</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3075,7 +3139,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3186,7 +3250,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1846.61</v>
+        <v>1569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3195,7 +3259,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3418,7 +3482,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1584.86</v>
+        <v>1525.53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3427,7 +3491,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3449,7 +3513,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3458,7 +3522,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1595.53</v>
+        <v>1611.29</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3467,7 +3531,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3949,7 +4013,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>❓ GB</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3958,7 +4022,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2413.23</v>
+        <v>2060.77</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +4031,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4894,7 +4958,7 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>2894.14</v>
+        <v>1675.9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4903,7 +4967,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4943,6 +5007,78 @@
         </is>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>183.249.5.117:22222</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>1935.13</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:08:36</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:08:36</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>103.30.31.59:20326</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>1714.98</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:08:36</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:08:36</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5071,7 +5207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5119,7 +5255,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5132,34 +5268,30 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>566.16</v>
+        <v>1793.03</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5174,32 +5306,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1832.39</v>
+        <v>566.16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5218,16 +5350,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1776.26</v>
+        <v>1608.13</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5239,7 +5371,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5254,32 +5386,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2428</v>
+        <v>1684.35</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5294,32 +5426,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2539.7</v>
+        <v>2428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5334,20 +5466,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1846.61</v>
+        <v>2539.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5359,7 +5491,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5374,20 +5506,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1584.86</v>
+        <v>1569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5399,7 +5531,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5414,32 +5546,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2108.46</v>
+        <v>1525.53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5454,32 +5586,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1220.39</v>
+        <v>1611.29</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5494,15 +5626,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>813.27</v>
+        <v>2108.46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5519,7 +5651,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5534,15 +5666,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>960.4400000000001</v>
+        <v>1220.39</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5559,7 +5691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5574,32 +5706,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1136.13</v>
+        <v>813.27</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5614,20 +5746,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2909.32</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5639,7 +5771,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5654,32 +5786,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1521.71</v>
+        <v>2060.77</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5694,32 +5826,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>706.86</v>
+        <v>1136.13</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5732,61 +5864,181 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>2729.47</v>
+        <v>2909.32</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>38.34.179.192:8451</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1521.71</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>38.145.208.191:8445</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>706.86</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>103.30.30.5:20326</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>2729.47</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>186.148.180.46:999</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E21" t="n">
         <v>1213.81</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>2026-03-28 16:49:31</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-03-28 16:49:31</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5803,7 +6055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5851,7 +6103,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5866,32 +6118,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>969.75</v>
+        <v>856.22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5906,32 +6158,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>856.22</v>
+        <v>894.51</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5946,32 +6198,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>894.51</v>
+        <v>525.63</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5986,63 +6238,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>525.63</v>
+        <v>1712.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>45.15.158.60:2222</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1712.6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -6081,7 +6293,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -6091,7 +6303,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -6101,7 +6313,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6111,7 +6323,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -6121,7 +6333,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -6131,7 +6343,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8">
@@ -6142,7 +6354,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:03:48</t>
+          <t>2026-03-28T17:08:36</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,20 +529,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>566.16</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,14 +552,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,37 +569,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>676.4400000000001</v>
+        <v>706.86</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,25 +609,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>706.86</v>
+        <v>767.73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -639,7 +635,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,16 +645,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>767.73</v>
+        <v>813.27</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,20 +685,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>813.27</v>
+        <v>856.22</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,37 +725,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>856.22</v>
+        <v>935.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -765,37 +761,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>894.51</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>148.222.152.4:999</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -810,16 +806,16 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>935.3</v>
+        <v>1042.88</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -841,30 +837,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>960.4400000000001</v>
+        <v>1043.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1123,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>47.91.65.23:3128</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1141,21 +1133,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>❓ DE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>1195.8</v>
+        <v>1170.55</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1287,7 +1283,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1297,21 +1293,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>1450.08</v>
+        <v>1244.61</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1333,25 +1333,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1502.59</v>
+        <v>1273.82</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1376,34 +1376,30 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1521.71</v>
+        <v>1339.76</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1413,25 +1409,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>1525.53</v>
+        <v>1450.08</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1443,7 +1435,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1453,33 +1445,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>❓ VN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>1541.47</v>
+        <v>1502.59</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1494,32 +1490,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1569</v>
+        <v>1521.71</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1534,15 +1530,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1608.13</v>
+        <v>1525.53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1559,7 +1555,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1569,37 +1565,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>1611.29</v>
+        <v>1541.47</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1609,16 +1601,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>1675.9</v>
+        <v>1569</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1635,7 +1631,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1654,11 +1650,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1684.35</v>
+        <v>1608.13</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1675,7 +1671,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1685,21 +1681,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>1695.07</v>
+        <v>1611.29</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1721,25 +1721,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1712.6</v>
+        <v>1675.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1751,7 +1747,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>103.30.31.59:20326</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1766,16 +1762,16 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>1714.98</v>
+        <v>1695.07</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1787,7 +1783,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1797,16 +1793,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>1782.81</v>
+        <v>1712.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1833,16 +1833,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1793.03</v>
+        <v>1714.98</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1869,25 +1869,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1895.98</v>
+        <v>1729.65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1914,28 +1914,28 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1905.25</v>
+        <v>1782.81</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1945,33 +1945,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>1907.03</v>
+        <v>1895.98</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1986,28 +1990,28 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1935.13</v>
+        <v>1905.25</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2022,7 +2026,7 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1949.35</v>
+        <v>1907.03</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2036,14 +2040,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2058,16 +2062,16 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>2035.82</v>
+        <v>1935.13</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2079,7 +2083,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>180.125.216.109:8118</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2094,28 +2098,28 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>2052.95</v>
+        <v>1949.35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2125,25 +2129,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>2060.77</v>
+        <v>2035.82</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2170,28 +2170,28 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>2106.89</v>
+        <v>2052.95</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2201,20 +2201,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2108.46</v>
+        <v>2106.89</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2231,7 +2227,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2241,33 +2237,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E48" t="n">
-        <v>2197.44</v>
+        <v>2108.46</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2282,16 +2282,16 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2220.89</v>
+        <v>2197.44</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2318,28 +2318,28 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>2236.82</v>
+        <v>2220.89</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2354,28 +2354,28 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2245.34</v>
+        <v>2236.82</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2385,37 +2385,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>2428</v>
+        <v>2245.34</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2425,37 +2421,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>❓ BR</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2430.36</v>
+        <v>2428</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2465,21 +2461,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="E54" t="n">
-        <v>2438.16</v>
+        <v>2430.36</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2567,7 +2567,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2577,25 +2577,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>❓ HK</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2715.84</v>
+        <v>2702</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2607,7 +2603,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2617,21 +2613,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>❓ HK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
       <c r="E58" t="n">
-        <v>2729.47</v>
+        <v>2715.84</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2656,34 +2656,30 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>2909.32</v>
+        <v>2729.47</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2693,33 +2689,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E60" t="n">
-        <v>2913.53</v>
+        <v>2909.32</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>45.188.167.25:999</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2734,19 +2734,55 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2763,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2862,7 +2898,7 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>1793.03</v>
+        <v>1339.76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2871,7 +2907,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2902,7 +2938,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>566.16</v>
+        <v>1273.82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2911,12 +2947,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2974,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2438.16</v>
+        <v>2702</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2947,7 +2983,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3010,7 +3046,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1195.8</v>
+        <v>1043.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3019,7 +3055,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3130,7 +3166,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1684.35</v>
+        <v>1729.65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3139,7 +3175,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4013,7 +4049,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4022,7 +4058,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2060.77</v>
+        <v>1244.61</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4031,7 +4067,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4089,16 +4125,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>894.51</v>
+        <v>1042.88</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4107,7 +4139,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5079,6 +5111,46 @@
         </is>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>47.91.65.23:3128</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>❓ DE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1170.55</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:15:13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:15:13</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5151,7 +5223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5160,39 +5232,32 @@
           <t>Прокси</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Рабочий</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Регион</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Страна</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Задержка (мс)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Дата добавления</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Последняя проверка</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>194.67.99.223:1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>86.53.183.16:1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5216,41 +5281,6 @@
           <t>Прокси</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Рабочий</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Регион</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Страна</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Задержка (мс)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Дата добавления</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Последняя проверка</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5258,35 +5288,6 @@
           <t>45.167.124.52:8080</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>1793.03</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-03-21 16:37:57</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5294,39 +5295,6 @@
           <t>147.161.210.140:8800</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>566.16</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-21 17:43:11</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>неизвестен</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5334,39 +5302,6 @@
           <t>167.103.31.122:8800</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1608.13</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-22 00:00:11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5374,39 +5309,6 @@
           <t>167.103.34.108:8800</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1684.35</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-22 11:24:40</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5414,39 +5316,6 @@
           <t>38.145.208.197:8445</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2428</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-22 19:15:48</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>неизвестен</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5454,39 +5323,6 @@
           <t>1.231.81.166:3128</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2539.7</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-24 16:40:38</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:49:31</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5494,553 +5330,116 @@
           <t>167.103.115.102:8800</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1569</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-24 17:37:29</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1525.53</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-26 23:28:37</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1611.29</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-27 03:25:45</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2108.46</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-27 17:31:32</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1220.39</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-28 03:45:15</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>813.27</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:35:01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>960.4400000000001</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-28 14:50:45</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>2060.77</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:28:28</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-03-28 17:08:36</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1136.13</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2909.32</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1521.71</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>706.86</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:06:43</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>proxymania</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="n">
-        <v>2729.47</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>38.145.208.191:8445</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>103.30.30.5:20326</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>45.15.158.60:2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>186.148.180.46:999</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1213.81</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:49:31</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:49:31</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -6055,7 +5454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6064,41 +5463,6 @@
           <t>Прокси</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Рабочий</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Регион</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Страна</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Задержка (мс)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Дата добавления</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Последняя проверка</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6106,77 +5470,11 @@
           <t>194.67.99.223:1080</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>856.22</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-03-26 19:33:10</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:26:45</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>894.51</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-28 15:52:24</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:49:31</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
     </row>
@@ -6186,77 +5484,11 @@
           <t>45.140.147.82:1082</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>525.63</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:03:06</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>thespeedx_http</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>45.15.158.60:2222</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1712.6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-03-28 16:44:58</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -6293,7 +5525,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -6303,7 +5535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -6323,7 +5555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -6343,7 +5575,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8">
@@ -6354,7 +5586,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:08:36</t>
+          <t>2026-03-28T17:15:13</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,37 +529,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>676.4400000000001</v>
+        <v>706.86</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>185.225.40.236:8080</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,25 +569,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>706.86</v>
+        <v>767.73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-27 22:00:25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -599,7 +595,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>185.225.40.236:8080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,16 +605,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>767.73</v>
+        <v>813.27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27 22:00:25</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,20 +645,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>813.27</v>
+        <v>856.22</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,14 +668,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>148.222.152.4:999</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,37 +685,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>856.22</v>
+        <v>935.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>148.222.152.4:999</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,33 +721,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>935.3</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 14:50:45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -766,32 +766,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>960.4400000000001</v>
+        <v>968.35</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28 14:50:45</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,21 +801,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>1042.88</v>
+        <v>1021.57</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -827,7 +831,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,11 +846,11 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>1043.9</v>
+        <v>1042.88</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1051,7 +1055,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1066,28 +1070,28 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1160.56</v>
+        <v>1144.19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1102,21 +1106,21 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1161.27</v>
+        <v>1160.56</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1167,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1173,25 +1177,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>1213.81</v>
+        <v>1182.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1218,32 +1218,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1220.39</v>
+        <v>1213.81</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1253,20 +1253,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1221.44</v>
+        <v>1220.39</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1293,37 +1293,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1244.61</v>
+        <v>1221.44</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1273.82</v>
+        <v>1244.61</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1376,13 +1376,17 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>1339.76</v>
+        <v>1273.82</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1399,7 +1403,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1409,21 +1413,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>1450.08</v>
+        <v>1383.07</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1435,7 +1443,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1445,25 +1453,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1502.59</v>
+        <v>1410.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1475,7 +1483,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1485,37 +1493,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>1521.71</v>
+        <v>1450.08</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>195.123.213.129:1080</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1525,25 +1529,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>1525.53</v>
+        <v>1485.27</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1565,33 +1565,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>❓ VN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>1541.47</v>
+        <v>1502.59</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1606,32 +1610,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1569</v>
+        <v>1521.71</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1646,15 +1650,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1608.13</v>
+        <v>1525.53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1671,7 +1675,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1681,37 +1685,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1611.29</v>
+        <v>1541.47</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1726,16 +1726,16 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1675.9</v>
+        <v>1557.23</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1757,21 +1757,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>1695.07</v>
+        <v>1608.13</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1783,7 +1787,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1793,25 +1797,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1712.6</v>
+        <v>1631.56</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1823,7 +1827,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>103.30.31.59:20326</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1838,11 +1842,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1714.98</v>
+        <v>1675.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1859,7 +1863,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1869,25 +1873,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1729.65</v>
+        <v>1695.07</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1909,16 +1909,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>1782.81</v>
+        <v>1712.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1935,7 +1939,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1945,25 +1949,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1895.98</v>
+        <v>1714.98</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1985,33 +1985,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E41" t="n">
-        <v>1905.25</v>
+        <v>1729.65</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2026,28 +2030,28 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1907.03</v>
+        <v>1782.81</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2062,28 +2066,28 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1935.13</v>
+        <v>1905.25</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2098,7 +2102,7 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1949.35</v>
+        <v>1907.03</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2112,14 +2116,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2134,16 +2138,16 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>2035.82</v>
+        <v>1935.13</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2155,7 +2159,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>180.125.216.109:8118</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2170,28 +2174,28 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>2052.95</v>
+        <v>1949.35</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2206,28 +2210,28 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2106.89</v>
+        <v>2035.82</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2237,37 +2241,33 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2108.46</v>
+        <v>2052.95</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2282,28 +2282,28 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2197.44</v>
+        <v>2106.89</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2313,33 +2313,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E50" t="n">
-        <v>2220.89</v>
+        <v>2108.46</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2354,28 +2358,28 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2236.82</v>
+        <v>2197.44</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2390,16 +2394,16 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>2245.34</v>
+        <v>2220.89</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2411,7 +2415,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2421,20 +2425,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2428</v>
+        <v>2236.82</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2461,16 +2461,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2430.36</v>
+        <v>2245.34</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2479,7 +2475,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2491,7 +2487,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2506,32 +2502,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2539.7</v>
+        <v>2428</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2541,33 +2537,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>❓ BR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="E56" t="n">
-        <v>2573.29</v>
+        <v>2430.36</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2577,21 +2577,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E57" t="n">
-        <v>2702</v>
+        <v>2501.93</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2603,7 +2607,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2613,20 +2617,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>❓ HK</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2715.84</v>
+        <v>2539.7</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2643,7 +2647,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2653,33 +2657,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>2729.47</v>
+        <v>2573.29</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2692,34 +2696,30 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>2909.32</v>
+        <v>2590.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2729,21 +2729,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>2913.53</v>
+        <v>2729.47</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2755,34 +2755,110 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>38.188.247.12:999</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
         </is>
@@ -2799,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2862,7 +2938,7 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>1161.27</v>
+        <v>1182.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2871,7 +2947,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2896,9 +2972,13 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>1339.76</v>
+        <v>968.35</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2907,7 +2987,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2974,7 +3054,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2702</v>
+        <v>1557.23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2983,7 +3063,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3046,7 +3126,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1043.9</v>
+        <v>1144.19</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3055,7 +3135,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3286,7 +3366,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1569</v>
+        <v>1383.07</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3295,7 +3375,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3469,16 +3549,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>❓ HK</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>2715.84</v>
+        <v>2590.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3487,7 +3563,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3549,7 +3625,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3558,7 +3634,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1611.29</v>
+        <v>1410.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3567,7 +3643,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3826,7 +3902,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1895.98</v>
+        <v>1631.56</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3835,7 +3911,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3906,7 +3982,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>676.4400000000001</v>
+        <v>2501.93</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3915,12 +3991,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -5151,6 +5227,82 @@
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>195.123.213.129:1080</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>1485.27</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:21:40</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:21:40</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1021.57</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:21:40</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:21:40</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5223,7 +5375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5258,6 +5410,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>45.15.158.60:2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5341,14 +5500,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
     </row>
@@ -5440,6 +5599,13 @@
       <c r="A24" t="inlineStr">
         <is>
           <t>186.148.180.46:999</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5489,6 +5655,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>45.15.158.60:2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5698,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -5535,7 +5708,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -5545,7 +5718,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -5565,7 +5738,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5575,7 +5748,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8">
@@ -5586,7 +5759,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:15:13</t>
+          <t>2026-03-28T17:21:40</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,7 +751,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,20 +761,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>968.35</v>
+        <v>1021.57</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>45.140.147.82:1081</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -801,25 +801,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>1021.57</v>
+        <v>1042.88</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -846,28 +842,28 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>1042.88</v>
+        <v>1068.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>45.144.28.81:10808</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -877,26 +873,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>1068.15</v>
+        <v>1083.38</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>144.124.227.90:21074</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -989,21 +989,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>1108.62</v>
+        <v>1098.02</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>144.124.227.90:21074</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1025,25 +1025,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>1136.13</v>
+        <v>1108.62</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1055,7 +1051,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1065,21 +1061,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>1144.19</v>
+        <v>1136.13</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1106,28 +1106,28 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1160.56</v>
+        <v>1144.19</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>47.91.65.23:3128</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1137,37 +1137,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>❓ DE</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1170.55</v>
+        <v>1160.56</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>47.91.65.23:3128</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1177,21 +1173,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>❓ DE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>1182.8</v>
+        <v>1170.55</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1213,25 +1213,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>1213.81</v>
+        <v>1182.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1403,7 +1399,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1418,20 +1414,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1383.07</v>
+        <v>1312.74</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1443,7 +1439,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1453,25 +1449,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>1410.7</v>
+        <v>1450.08</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1483,7 +1475,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1493,33 +1485,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>1450.08</v>
+        <v>1521.71</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>195.123.213.129:1080</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1534,28 +1530,28 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>1485.27</v>
+        <v>1541.47</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1565,25 +1561,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1502.59</v>
+        <v>1608.13</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1595,7 +1591,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1605,37 +1601,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1521.71</v>
+        <v>1617.12</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1645,25 +1641,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1525.53</v>
+        <v>1631.56</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1675,7 +1671,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1690,28 +1686,28 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1541.47</v>
+        <v>1675.9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1726,16 +1722,16 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1557.23</v>
+        <v>1695.07</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1747,7 +1743,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1757,25 +1753,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1608.13</v>
+        <v>1712.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1787,7 +1783,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1797,25 +1793,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>1631.56</v>
+        <v>1714.98</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1827,7 +1819,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1837,21 +1829,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>1675.9</v>
+        <v>1729.65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1863,7 +1859,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1873,21 +1869,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>1695.07</v>
+        <v>1748.94</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1909,25 +1909,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>❓ NL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1712.6</v>
+        <v>1788.37</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>103.30.31.59:20326</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1949,21 +1949,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>❓ PH</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>1714.98</v>
+        <v>1869.75</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1975,7 +1979,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1985,37 +1989,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1729.65</v>
+        <v>1905.25</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2030,28 +2030,28 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1782.81</v>
+        <v>1907.03</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2066,28 +2066,28 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1905.25</v>
+        <v>1935.13</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1907.03</v>
+        <v>1949.35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2133,21 +2133,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>1935.13</v>
+        <v>1982.05</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2159,7 +2163,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2169,33 +2173,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>1949.35</v>
+        <v>1987.87</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>195.123.213.129:1080</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2210,16 +2218,16 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2035.82</v>
+        <v>2012.27</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2231,7 +2239,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>180.125.216.109:8118</t>
+          <t>119.18.145.50:30226</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2246,16 +2254,16 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2052.95</v>
+        <v>2019.03</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2267,7 +2275,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2282,28 +2290,28 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2106.89</v>
+        <v>2035.82</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2313,37 +2321,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>2108.46</v>
+        <v>2052.95</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2358,16 +2362,16 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2197.44</v>
+        <v>2085.7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2379,7 +2383,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2394,28 +2398,28 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>2220.89</v>
+        <v>2106.89</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2425,16 +2429,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E53" t="n">
-        <v>2236.82</v>
+        <v>2108.46</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2466,7 +2474,7 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2245.34</v>
+        <v>2187.88</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2475,7 +2483,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2487,7 +2495,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2497,37 +2505,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2428</v>
+        <v>2197.44</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2537,25 +2541,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>2430.36</v>
+        <v>2220.89</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2567,7 +2567,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2577,37 +2577,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>❓ NL</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2501.93</v>
+        <v>2236.82</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2622,32 +2618,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2539.7</v>
+        <v>2428</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2657,33 +2653,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E59" t="n">
-        <v>2573.29</v>
+        <v>2539.7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2693,33 +2693,33 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>2590.5</v>
+        <v>2573.29</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2734,16 +2734,16 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>2729.47</v>
+        <v>2590.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2755,7 +2755,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2765,37 +2765,33 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>2909.32</v>
+        <v>2666.14</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>181.78.44.243:999</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2810,16 +2806,16 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>2913.53</v>
+        <v>2708.98</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2831,7 +2827,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2841,26 +2837,174 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
+        <v>2729.47</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:44:58</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
         <v>2926.76</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>2026-03-28 16:06:43</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>78.134.20.48:8080</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>2982.19</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -2875,7 +3019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2972,13 +3116,9 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>968.35</v>
+        <v>1098.02</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2987,7 +3127,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3054,7 +3194,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>1557.23</v>
+        <v>2085.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3063,7 +3203,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3085,12 +3225,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>❓ PH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>1782.81</v>
+        <v>1869.75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3099,7 +3243,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3197,7 +3341,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>❓ VN</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3206,7 +3350,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1502.59</v>
+        <v>1987.87</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3215,7 +3359,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3366,7 +3510,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1383.07</v>
+        <v>1982.05</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3375,7 +3519,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3594,7 +3738,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1525.53</v>
+        <v>1748.94</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3603,7 +3747,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3634,7 +3778,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1410.7</v>
+        <v>1617.12</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3643,7 +3787,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3982,7 +4126,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2501.93</v>
+        <v>1788.37</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3991,7 +4135,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4694,7 +4838,7 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2245.34</v>
+        <v>2187.88</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4703,7 +4847,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4761,16 +4905,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>❓ BR</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>2430.36</v>
+        <v>2666.14</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4779,7 +4919,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4958,7 +5098,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1213.81</v>
+        <v>1312.74</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4967,7 +5107,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5250,7 +5390,7 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>1485.27</v>
+        <v>2012.27</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5259,7 +5399,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5303,6 +5443,154 @@
         </is>
       </c>
       <c r="H64" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>181.78.44.243:999</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>2708.98</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>119.18.145.50:30226</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>2019.03</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>78.134.20.48:8080</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>2982.19</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>45.144.28.81:10808</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1083.38</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:30:52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5431,7 +5719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5465,145 +5753,152 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>45.140.147.82:1082</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>186.148.180.46:999</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>45.140.147.82:1081</t>
         </is>
@@ -5698,7 +5993,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -5708,7 +6003,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -5728,7 +6023,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -5748,7 +6043,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8">
@@ -5759,7 +6054,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:21:40</t>
+          <t>2026-03-28T17:30:52</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,7 +1091,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1106,28 +1106,28 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1144.19</v>
+        <v>1160.56</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>47.91.65.23:3128</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1137,33 +1137,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>❓ DE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>1160.56</v>
+        <v>1170.55</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>47.91.65.23:3128</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1173,25 +1177,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ DE</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>1170.55</v>
+        <v>1182.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1213,33 +1213,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>1182.8</v>
+        <v>1220.39</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1249,20 +1253,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ SG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1220.39</v>
+        <v>1221.44</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1279,7 +1283,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1289,37 +1293,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1221.44</v>
+        <v>1244.61</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1329,25 +1333,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1244.61</v>
+        <v>1302.59</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1359,7 +1363,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1374,20 +1378,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1273.82</v>
+        <v>1312.74</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1399,7 +1403,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1409,25 +1413,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>1312.74</v>
+        <v>1450.08</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1449,33 +1449,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>1450.08</v>
+        <v>1521.71</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1485,25 +1489,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>1521.71</v>
+        <v>1541.47</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1525,33 +1525,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E29" t="n">
-        <v>1541.47</v>
+        <v>1601.22</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1566,20 +1570,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1608.13</v>
+        <v>1671.25</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1591,7 +1595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1601,25 +1605,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>1617.12</v>
+        <v>1675.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1641,25 +1641,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>1631.56</v>
+        <v>1682.41</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1671,7 +1667,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1686,16 +1682,16 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1675.9</v>
+        <v>1695.07</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1707,7 +1703,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1717,21 +1713,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>1695.07</v>
+        <v>1712.6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1753,25 +1753,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>1712.6</v>
+        <v>1714.98</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1783,7 +1779,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>103.30.31.59:20326</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1793,21 +1789,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>1714.98</v>
+        <v>1748.94</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1829,25 +1829,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ PH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1729.65</v>
+        <v>1869.75</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1869,37 +1869,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1748.94</v>
+        <v>1905.25</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1909,37 +1905,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>❓ NL</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1788.37</v>
+        <v>1907.03</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1949,25 +1941,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1869.75</v>
+        <v>1935.13</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1979,7 +1967,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1989,33 +1977,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E41" t="n">
-        <v>1905.25</v>
+        <v>1942.9</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2030,7 +2022,7 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1907.03</v>
+        <v>1949.35</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2044,14 +2036,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2061,21 +2053,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E43" t="n">
-        <v>1935.13</v>
+        <v>1981.69</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2087,7 +2083,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2097,33 +2093,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E44" t="n">
-        <v>1949.35</v>
+        <v>1982.05</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2138,15 +2138,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1982.05</v>
+        <v>1987.87</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>195.123.213.129:1080</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2173,20 +2173,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1987.87</v>
+        <v>2012.27</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2203,7 +2199,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>195.123.213.129:1080</t>
+          <t>119.18.145.50:30226</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2218,11 +2214,11 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2012.27</v>
+        <v>2019.03</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2239,7 +2235,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>119.18.145.50:30226</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2254,16 +2250,16 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2019.03</v>
+        <v>2035.82</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2275,7 +2271,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2285,21 +2281,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E49" t="n">
-        <v>2035.82</v>
+        <v>2049.52</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2362,28 +2362,28 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2085.7</v>
+        <v>2106.89</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2393,16 +2393,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E52" t="n">
-        <v>2106.89</v>
+        <v>2108.46</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2419,7 +2423,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2429,37 +2433,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2108.46</v>
+        <v>2187.88</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2474,16 +2474,16 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2187.88</v>
+        <v>2197.44</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2510,16 +2510,16 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2197.44</v>
+        <v>2220.89</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2546,28 +2546,28 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>2220.89</v>
+        <v>2236.82</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2577,33 +2577,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E57" t="n">
-        <v>2236.82</v>
+        <v>2337.39</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2613,37 +2617,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2428</v>
+        <v>2366.51</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2658,32 +2662,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2539.7</v>
+        <v>2428</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2698,28 +2702,28 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>2573.29</v>
+        <v>2519.3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2732,18 +2736,22 @@
           <t>🇺🇸 США</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E61" t="n">
-        <v>2590.5</v>
+        <v>2539.7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2755,7 +2763,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2770,28 +2778,28 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>2666.14</v>
+        <v>2573.29</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>181.78.44.243:999</t>
+          <t>93.91.112.247:41258</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2806,16 +2814,16 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>2708.98</v>
+        <v>2659.39</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2827,7 +2835,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2837,21 +2845,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>2729.47</v>
+        <v>2666.14</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2863,7 +2871,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>181.78.44.243:999</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2873,37 +2881,33 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>2909.32</v>
+        <v>2708.98</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2913,21 +2917,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>2913.53</v>
+        <v>2729.47</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2939,7 +2943,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2949,33 +2953,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E67" t="n">
-        <v>2926.76</v>
+        <v>2909.32</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>78.134.20.48:8080</t>
+          <t>45.188.167.25:999</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2990,19 +2998,91 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>2926.76</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>78.134.20.48:8080</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
         <v>2982.19</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -3019,7 +3099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3158,7 +3238,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1273.82</v>
+        <v>1671.25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3167,7 +3247,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3194,7 +3274,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2085.7</v>
+        <v>2519.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3203,7 +3283,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3270,7 +3350,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1144.19</v>
+        <v>1682.41</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3279,7 +3359,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3310,7 +3390,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1608.13</v>
+        <v>1981.69</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3319,7 +3399,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3390,7 +3470,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1729.65</v>
+        <v>1942.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3399,7 +3479,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3693,12 +3773,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>❓ HK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>2590.5</v>
+        <v>2366.51</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3707,7 +3791,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3778,7 +3862,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1617.12</v>
+        <v>2049.52</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3787,7 +3871,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4046,7 +4130,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1631.56</v>
+        <v>2337.39</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4055,7 +4139,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4117,7 +4201,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,7 +4210,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1788.37</v>
+        <v>1302.59</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4135,7 +4219,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5591,6 +5675,82 @@
         </is>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>93.91.112.247:41258</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>2659.39</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:41:44</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:41:44</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1082</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1601.22</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:41:44</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:41:44</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5663,7 +5823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5705,6 +5865,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5795,35 +5962,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
     </row>
@@ -5901,6 +6068,13 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
     </row>
@@ -5915,7 +6089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5957,6 +6131,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>45.140.147.82:1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
     </row>
@@ -5993,7 +6174,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -6003,7 +6184,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -6013,7 +6194,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6033,7 +6214,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -6043,7 +6224,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -6054,7 +6235,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:30:52</t>
+          <t>2026-03-28T17:41:44</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все прокси" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рабочие" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нерабочие" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Российские" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Американские" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Российские (только)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Американские (только)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Глобальные" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статистика" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>101.251.204.174:8080</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -806,28 +806,28 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>1042.88</v>
+        <v>1068.15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 05:14:59</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>101.251.204.174:8080</t>
+          <t>45.144.28.81:10808</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -837,33 +837,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>❓ NL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>1068.15</v>
+        <v>1083.38</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28 05:14:59</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>45.144.28.81:10808</t>
+          <t>120.92.212.16:7890</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -873,37 +877,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>❓ NL</t>
+          <t>❓ CN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1083.38</v>
+        <v>1087.57</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-26 17:05:06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_socks5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>120.92.212.16:7890</t>
+          <t>120.92.211.211:7890</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -913,37 +917,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>❓ CN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>1087.57</v>
+        <v>1089.35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-26 17:05:06</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>thespeedx_socks5</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>120.92.211.211:7890</t>
+          <t>144.124.227.90:21074</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -958,28 +958,28 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>1089.35</v>
+        <v>1108.62</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -989,21 +989,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>1098.02</v>
+        <v>1136.13</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1015,7 +1019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>144.124.227.90:21074</t>
+          <t>103.156.15.210:1111</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1030,28 +1034,28 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>1108.62</v>
+        <v>1160.56</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>47.91.65.23:3128</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1061,25 +1065,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ DE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1136.13</v>
+        <v>1170.55</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1091,7 +1095,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>103.156.15.210:1111</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1106,28 +1110,28 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1160.56</v>
+        <v>1182.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>47.91.65.23:3128</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1137,37 +1141,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>❓ DE</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1170.55</v>
+        <v>1220.39</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1177,33 +1181,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>1182.8</v>
+        <v>1221.44</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1213,37 +1221,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1220.39</v>
+        <v>1244.61</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:15:13</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1253,37 +1261,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>❓ SG</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1221.44</v>
+        <v>1302.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1293,25 +1301,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1244.61</v>
+        <v>1312.74</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1323,7 +1331,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1333,25 +1341,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1302.59</v>
+        <v>1450.08</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1363,7 +1367,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1373,25 +1377,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312.74</v>
+        <v>1485.81</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1403,7 +1407,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1413,33 +1417,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>1450.08</v>
+        <v>1521.71</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>120.92.212.16:8890</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1449,25 +1457,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>1521.71</v>
+        <v>1541.47</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1479,7 +1483,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>120.92.212.16:8890</t>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1489,33 +1493,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>1541.47</v>
+        <v>1601.22</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>45.140.147.155:1082</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1525,20 +1533,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1601.22</v>
+        <v>1671.25</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1555,7 +1563,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1565,25 +1573,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>1671.25</v>
+        <v>1675.9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1595,7 +1599,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1610,16 +1614,16 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>1675.9</v>
+        <v>1695.07</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1631,7 +1635,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1641,21 +1645,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E32" t="n">
-        <v>1682.41</v>
+        <v>1712.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1667,7 +1675,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1682,16 +1690,16 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>1695.07</v>
+        <v>1714.98</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1703,7 +1711,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1713,25 +1721,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1712.6</v>
+        <v>1736.57</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1743,7 +1751,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>103.30.31.59:20326</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1753,21 +1761,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>1714.98</v>
+        <v>1748.94</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1779,7 +1791,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1789,25 +1801,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1748.94</v>
+        <v>1818.69</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1819,7 +1831,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1829,25 +1841,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>1869.75</v>
+        <v>1829.48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1859,7 +1867,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1869,33 +1877,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>1905.25</v>
+        <v>1850.46</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>103.152.140.182:8090</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1905,33 +1917,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1907.03</v>
+        <v>1885.76</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1946,28 +1958,28 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1935.13</v>
+        <v>1905.25</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1977,37 +1989,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1942.9</v>
+        <v>1907.03</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>43.225.151.174:43030</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2022,28 +2030,28 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1949.35</v>
+        <v>1919.6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2053,7 +2061,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2062,11 +2070,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1981.69</v>
+        <v>1942.9</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2083,7 +2091,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2093,37 +2101,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1982.05</v>
+        <v>1949.35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2133,25 +2137,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1987.87</v>
+        <v>1981.69</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2163,7 +2167,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>195.123.213.129:1080</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2173,16 +2177,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>2012.27</v>
+        <v>1987.87</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2199,7 +2207,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>119.18.145.50:30226</t>
+          <t>195.123.213.129:1080</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2214,11 +2222,11 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2019.03</v>
+        <v>2012.27</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2235,7 +2243,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>119.18.145.50:30226</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2250,16 +2258,16 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2035.82</v>
+        <v>2019.03</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2271,7 +2279,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2281,25 +2289,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2049.52</v>
+        <v>2035.82</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2423,7 +2427,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2438,16 +2442,16 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2187.88</v>
+        <v>2131.2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2459,7 +2463,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2474,16 +2478,16 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2197.44</v>
+        <v>2187.88</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2495,7 +2499,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2510,16 +2514,16 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2220.89</v>
+        <v>2197.44</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2531,7 +2535,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2546,28 +2550,28 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>2236.82</v>
+        <v>2220.89</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>180.250.219.58:53281</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2577,25 +2581,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2337.39</v>
+        <v>2234.67</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28 14:31:30</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2607,7 +2607,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2617,37 +2617,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>❓ HK</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>2366.51</v>
+        <v>2236.82</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2657,37 +2653,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ ID</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2428</v>
+        <v>2321.24</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>180.250.219.58:53281</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2697,16 +2693,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>❓ ID</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E60" t="n">
-        <v>2519.3</v>
+        <v>2337.39</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 14:31:30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2539.7</v>
+        <v>2428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2773,33 +2773,33 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>2573.29</v>
+        <v>2466.19</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>93.91.112.247:41258</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2809,21 +2809,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
       <c r="E63" t="n">
-        <v>2659.39</v>
+        <v>2519.03</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2835,7 +2839,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2850,28 +2854,28 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>2666.14</v>
+        <v>2573.29</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>181.78.44.243:999</t>
+          <t>93.91.112.247:41258</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2886,16 +2890,16 @@
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>2708.98</v>
+        <v>2659.39</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2907,7 +2911,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2917,21 +2921,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>2729.47</v>
+        <v>2666.14</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2943,7 +2947,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>181.78.44.243:999</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2953,37 +2957,33 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>2909.32</v>
+        <v>2708.98</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2993,21 +2993,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>2913.53</v>
+        <v>2729.47</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3029,33 +3029,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E69" t="n">
-        <v>2926.76</v>
+        <v>2909.32</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:03:06</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>78.134.20.48:8080</t>
+          <t>45.188.167.25:999</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3070,19 +3074,91 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>2926.76</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>78.134.20.48:8080</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
         <v>2982.19</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -3099,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3193,12 +3269,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>1098.02</v>
+        <v>1736.57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3207,7 +3287,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3229,7 +3309,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3274,7 +3354,7 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2519.3</v>
+        <v>1829.48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3283,7 +3363,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3305,16 +3385,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ PH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>1869.75</v>
+        <v>2131.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3323,7 +3399,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3350,7 +3426,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1682.41</v>
+        <v>2234.67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3359,7 +3435,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3381,7 +3457,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3421,7 +3497,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3461,7 +3537,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3501,7 +3577,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3541,7 +3617,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3550,7 +3626,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2539.7</v>
+        <v>2519.03</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3559,7 +3635,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3581,7 +3657,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3590,7 +3666,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1982.05</v>
+        <v>1818.69</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3599,7 +3675,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3782,7 +3858,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2366.51</v>
+        <v>1485.81</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3791,7 +3867,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3813,7 +3889,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3862,7 +3938,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2049.52</v>
+        <v>2321.24</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3871,7 +3947,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3893,7 +3969,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3969,7 +4045,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4161,7 +4237,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4201,7 +4277,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4241,7 +4317,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4429,12 +4505,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E35" t="n">
-        <v>1042.88</v>
+        <v>1850.46</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4443,7 +4523,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:15:13</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4465,7 +4545,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4505,7 +4585,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4621,7 +4701,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4697,7 +4777,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5025,7 +5105,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5173,7 +5253,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5357,12 +5437,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>1935.13</v>
+        <v>2466.19</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5371,7 +5451,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5751,6 +5831,78 @@
         </is>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>103.152.140.182:8090</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>1885.76</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:44:16</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:44:16</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>43.225.151.174:43030</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>1919.6</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:44:16</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-03-28 17:44:16</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -5823,7 +5975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,42 +5988,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>86.53.183.16:1080</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1082</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>45.15.158.60:2222</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1081</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>45.140.147.155:1082</t>
+          <t>Нет прокси</t>
         </is>
       </c>
     </row>
@@ -5886,7 +6003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5955,126 +6072,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45.140.147.82:1082</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>186.148.180.46:999</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>45.140.147.82:1081</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>45.140.147.155:1082</t>
+          <t>103.152.140.182:8090</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6270,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -6184,33 +6280,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Российских</t>
+          <t>Российские (только РФ)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Американских</t>
+          <t>Американские (только США)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Глобальных</t>
+          <t>Глобальные (РФ+США)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6224,7 +6320,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8">
@@ -6235,7 +6331,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:41:44</t>
+          <t>2026-03-28T17:44:16</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1331,7 +1331,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1450.08</v>
+        <v>1317.76</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>103.84.95.54:7890</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1377,25 +1377,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>❓ HK</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1485.81</v>
+        <v>1450.08</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26 22:18:34</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1483,7 +1479,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>45.140.147.155:1082</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1493,25 +1489,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1601.22</v>
+        <v>1599.62</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1523,7 +1519,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1533,20 +1529,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1671.25</v>
+        <v>1601.22</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1563,7 +1559,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>210.87.125.57:8080</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1573,21 +1569,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>1675.9</v>
+        <v>1642.03</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>210.87.125.57:8080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1614,16 +1614,16 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>1695.07</v>
+        <v>1675.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45.15.158.60:2222</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1645,25 +1645,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>1712.6</v>
+        <v>1695.07</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1675,7 +1671,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>103.30.31.59:20326</t>
+          <t>45.15.158.60:2222</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1685,21 +1681,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>🌍 Глобальный</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>1714.98</v>
+        <v>1712.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45.167.124.52:8080</t>
+          <t>103.30.31.59:20326</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1721,25 +1721,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1736.57</v>
+        <v>1714.98</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1748.94</v>
+        <v>1731.97</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1779,7 +1775,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1791,7 +1787,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>45.167.124.52:8080</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1806,15 +1802,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1818.69</v>
+        <v>1736.57</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1831,7 +1827,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20.24.43.214:80</t>
+          <t>167.71.196.28:8080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1841,21 +1837,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>1829.48</v>
+        <v>1778.53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-21 18:39:26</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1867,7 +1867,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>163.5.128.210:14270</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1877,25 +1877,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1850.46</v>
+        <v>1779.48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1907,7 +1903,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>103.152.140.182:8090</t>
+          <t>103.84.95.54:7890</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1917,21 +1913,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>❓ HK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>1885.76</v>
+        <v>1810.11</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-26 22:18:34</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1953,33 +1953,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>1905.25</v>
+        <v>1818.69</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>20.24.43.214:80</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1994,28 +1998,28 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1907.03</v>
+        <v>1829.48</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-21 18:39:26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>43.225.151.174:43030</t>
+          <t>103.152.140.182:8090</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2025,12 +2029,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1919.6</v>
+        <v>1885.76</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2051,7 +2055,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2061,37 +2065,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1942.9</v>
+        <v>1905.25</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>167.103.31.122:8800</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2101,33 +2101,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E44" t="n">
-        <v>1949.35</v>
+        <v>1905.84</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-22 00:00:11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>167.103.31.122:8800</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2137,37 +2141,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1981.69</v>
+        <v>1907.03</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-22 00:00:11</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>43.225.151.174:43030</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2177,25 +2177,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1987.87</v>
+        <v>1919.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2207,7 +2203,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>195.123.213.129:1080</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2217,21 +2213,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>2012.27</v>
+        <v>1942.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>119.18.145.50:30226</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2258,28 +2258,28 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2019.03</v>
+        <v>1949.35</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>195.123.213.129:1080</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2294,16 +2294,16 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2035.82</v>
+        <v>2012.27</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>180.125.216.109:8118</t>
+          <t>119.18.145.50:30226</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2330,16 +2330,16 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>2052.95</v>
+        <v>2019.03</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2366,28 +2366,28 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>2106.89</v>
+        <v>2035.82</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2402,32 +2402,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2108.46</v>
+        <v>2046.28</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>180.125.216.109:8118</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2131.2</v>
+        <v>2052.95</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2478,28 +2478,28 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2187.88</v>
+        <v>2106.89</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2509,33 +2509,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E55" t="n">
-        <v>2197.44</v>
+        <v>2108.46</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2550,16 +2554,16 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>2220.89</v>
+        <v>2187.88</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2571,7 +2575,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2586,16 +2590,16 @@
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2234.67</v>
+        <v>2197.44</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2607,7 +2611,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2622,28 +2626,28 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>2236.82</v>
+        <v>2220.89</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:26:45</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2653,30 +2657,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>❓ ID</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>2321.24</v>
+        <v>2236.82</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 16:26:45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>93.91.112.247:41258</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2885,21 +2885,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="E65" t="n">
-        <v>2659.39</v>
+        <v>2591.49</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2911,7 +2915,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>109.135.16.145:8789</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2926,16 +2930,16 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>2666.14</v>
+        <v>2627.64</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2947,7 +2951,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>181.78.44.243:999</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2957,21 +2961,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>❓ PH</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
       <c r="E67" t="n">
-        <v>2708.98</v>
+        <v>2634.86</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2983,7 +2991,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>93.91.112.247:41258</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2993,21 +3001,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
+          <t>❓ Неизвестно</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>2729.47</v>
+        <v>2659.39</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3019,7 +3027,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3029,37 +3037,33 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>🇺🇸 США (только)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>2909.32</v>
+        <v>2666.14</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>181.78.44.243:999</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3074,16 +3078,16 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>2913.53</v>
+        <v>2708.98</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3095,7 +3099,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3105,60 +3109,172 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>2926.76</v>
+        <v>2729.47</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>🇺🇸 США (только)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>2926.76</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>78.134.20.48:8080</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>✅ Да</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="n">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
         <v>2982.19</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -3175,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3318,7 +3434,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1671.25</v>
+        <v>1599.62</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3327,7 +3443,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3385,12 +3501,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>❓ Неизвестно</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>❓ PH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>2131.2</v>
+        <v>2634.86</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3399,7 +3519,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3426,7 +3546,7 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2234.67</v>
+        <v>1317.76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3435,7 +3555,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3466,7 +3586,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1981.69</v>
+        <v>1905.84</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3475,7 +3595,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3506,7 +3626,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1987.87</v>
+        <v>2046.28</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3515,7 +3635,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3858,7 +3978,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1485.81</v>
+        <v>1810.11</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3867,7 +3987,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3898,7 +4018,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1748.94</v>
+        <v>1731.97</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3907,7 +4027,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3929,7 +4049,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>❓ ID</t>
+          <t>🇺🇸 США (только)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3938,7 +4058,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2321.24</v>
+        <v>1642.03</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3947,7 +4067,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4514,7 +4634,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1850.46</v>
+        <v>2591.49</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4523,7 +4643,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5903,6 +6023,118 @@
         </is>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>163.5.128.210:14270</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>1779.48</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:04:33</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:04:33</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>109.135.16.145:8789</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>❓ Неизвестно</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>2627.64</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:04:33</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:04:33</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>167.71.196.28:8080</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>✅ Да</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>❓ SG</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1778.53</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:04:33</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:04:33</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -6003,7 +6235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6079,96 +6311,103 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>177.234.217.88:999</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>177.234.217.88:999</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>194.59.204.87:9080</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>194.59.204.87:9080</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>38.34.179.192:8451</t>
+          <t>38.145.220.13:8444</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>38.145.208.191:8445</t>
+          <t>38.34.179.192:8451</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>38.145.208.191:8445</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
+        <is>
+          <t>183.249.5.117:22222</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>103.152.140.182:8090</t>
         </is>
@@ -6270,7 +6509,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -6280,7 +6519,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -6300,7 +6539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -6320,7 +6559,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8">
@@ -6331,7 +6570,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:44:16</t>
+          <t>2026-03-28T18:04:33</t>
         </is>
       </c>
     </row>

--- a/reports/proxy_report.xlsx
+++ b/reports/proxy_report.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -791,11 +791,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>144.124.227.90:21074</t>
+          <t>5.102.109.41:999</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1108.62</v>
+        <v>1100.52</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-28 18:27:49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -821,20 +821,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>217.76.245.80:999</t>
+          <t>144.124.227.90:21074</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1136.13</v>
+        <v>1108.62</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -846,25 +851,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15.188.75.223:3128</t>
+          <t>217.76.245.80:999</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1153.89</v>
+        <v>1136.13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-21 16:37:57</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -936,50 +936,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38.145.218.76:8451</t>
+          <t>15.188.75.223:3128</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1220.39</v>
+        <v>1186.78</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-28 03:45:15</t>
+          <t>2026-03-21 16:37:57</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>128.199.114.189:9090</t>
+          <t>38.145.218.76:8451</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1221.44</v>
+        <v>1220.39</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Singapore</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-28 11:16:32</t>
+          <t>2026-03-28 03:45:15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -991,36 +991,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>86.53.183.16:1080</t>
+          <t>128.199.114.189:9090</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1244.61</v>
+        <v>1221.44</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 11:16:32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45.140.147.82:1081</t>
+          <t>86.53.183.16:1080</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1255.16</v>
+        <v>1244.61</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1029,7 +1034,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1041,25 +1046,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13.230.49.39:8080</t>
+          <t>45.140.147.82:1081</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1317.76</v>
+        <v>1255.16</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03-21 21:12:45</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1071,20 +1071,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>194.67.99.223:1080</t>
+          <t>13.230.49.39:8080</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1441.07</v>
+        <v>1317.76</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-26 19:33:10</t>
+          <t>2026-03-21 21:12:45</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1096,25 +1101,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>150.107.140.238:3128</t>
+          <t>194.67.99.223:1080</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1450.08</v>
+        <v>1441.07</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-26 19:33:10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1126,20 +1126,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>64.227.76.27:1080</t>
+          <t>150.107.140.238:3128</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1450.12</v>
+        <v>1450.08</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-28 14:35:01</t>
+          <t>2026-03-28 16:06:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1206,20 +1211,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>147.161.210.140:8800</t>
+          <t>45.140.147.155:1082</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1599.62</v>
+        <v>1601.22</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌍 Глобальный</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-21 17:43:11</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1231,20 +1236,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>45.140.147.155:1082</t>
+          <t>147.161.210.140:8800</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1601.22</v>
+        <v>1621.18</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🌍 Глобальный</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-21 17:43:11</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1256,11 +1261,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16.78.119.130:443</t>
+          <t>167.103.34.108:8800</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1642.03</v>
+        <v>1652.22</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1269,7 +1274,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-27 03:25:45</t>
+          <t>2026-03-22 11:24:40</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1366,20 +1371,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>167.103.144.127:8800</t>
+          <t>8.212.177.126:8080</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1731.97</v>
+        <v>1754.75</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-26 23:28:37</t>
+          <t>2026-03-21 19:33:29</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1391,11 +1401,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8.212.177.126:8080</t>
+          <t>16.78.119.130:443</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1754.75</v>
+        <v>1759.71</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1404,12 +1414,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-21 19:33:29</t>
+          <t>2026-03-27 03:25:45</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1425,7 +1435,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1764.33</v>
+        <v>1775.64</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1566,11 +1576,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>167.103.115.102:8800</t>
+          <t>103.152.140.182:8090</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1818.69</v>
+        <v>1885.76</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1579,7 +1589,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-24 17:37:29</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1591,36 +1601,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>103.152.140.182:8090</t>
+          <t>106.75.15.167:7890</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1885.76</v>
+        <v>1905.25</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-26 17:22:48</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>106.75.15.167:7890</t>
+          <t>158.160.215.167:8123</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1905.25</v>
+        <v>1907.03</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1634,7 +1649,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-26 17:22:48</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1646,50 +1661,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>158.160.215.167:8123</t>
+          <t>183.249.5.117:22222</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1907.03</v>
+        <v>1910.93</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-28 17:08:36</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>183.249.5.117:22222</t>
+          <t>43.99.54.236:5555</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1910.93</v>
+        <v>1922.61</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-28 17:08:36</t>
+          <t>2026-03-26 20:03:49</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1701,25 +1716,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>43.99.54.236:5555</t>
+          <t>167.103.144.127:8800</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1922.61</v>
+        <v>1929.31</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-03-26 20:03:49</t>
+          <t>2026-03-26 23:28:37</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1731,55 +1741,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>167.103.34.108:8800</t>
+          <t>185.76.240.44:10001</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1942.9</v>
+        <v>1949.35</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-03-22 11:24:40</t>
+          <t>2026-03-28 15:28:28</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>185.76.240.44:10001</t>
+          <t>167.103.115.102:8800</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1949.35</v>
+        <v>1958.91</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-03-28 15:28:28</t>
+          <t>2026-03-24 17:37:29</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
@@ -1816,11 +1826,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>195.123.213.129:1080</t>
+          <t>59.153.16.105:20909</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2012.27</v>
+        <v>1976.7</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1834,7 +1844,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-28 17:21:40</t>
+          <t>2026-03-28 18:27:49</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1846,11 +1856,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>119.18.145.50:30226</t>
+          <t>195.123.213.129:1080</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2019.03</v>
+        <v>2012.27</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1864,7 +1874,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 17:21:40</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1876,11 +1886,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>202.154.18.80:8082</t>
+          <t>119.18.145.50:30226</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2035.82</v>
+        <v>2019.03</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1894,7 +1904,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1906,20 +1916,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>113.160.132.26:8080</t>
+          <t>202.154.18.80:8082</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2046.28</v>
+        <v>2035.82</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-22 07:23:44</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1961,11 +1976,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>128.199.254.13:9090</t>
+          <t>113.160.132.26:8080</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2106.89</v>
+        <v>2066.86</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1974,37 +1989,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Неизвестно</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-28 11:46:50</t>
+          <t>2026-03-22 07:23:44</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>38.145.208.189:8449</t>
+          <t>128.199.254.13:9090</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2108.46</v>
+        <v>2106.89</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-27 17:31:32</t>
+          <t>2026-03-28 11:46:50</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2016,11 +2036,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>207.254.71.62:8088</t>
+          <t>38.145.208.189:8449</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2176.63</v>
+        <v>2108.46</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2029,37 +2049,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-03-28 18:12:24</t>
+          <t>2026-03-27 17:31:32</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>59.46.216.131:30001</t>
+          <t>207.254.71.62:8088</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2187.88</v>
+        <v>2176.63</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 18:12:24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2071,11 +2086,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>117.50.7.101:8000</t>
+          <t>59.46.216.131:30001</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2197.44</v>
+        <v>2187.88</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2089,7 +2104,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2101,11 +2116,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5.104.87.17:8051</t>
+          <t>117.50.7.101:8000</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2220.89</v>
+        <v>2197.44</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2119,7 +2134,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-28 17:03:48</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2131,11 +2146,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>113.11.97.193:30226</t>
+          <t>5.104.87.17:8051</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2236.82</v>
+        <v>2220.89</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2149,57 +2164,67 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-03-28 15:41:05</t>
+          <t>2026-03-28 17:03:48</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>38.145.208.197:8445</t>
+          <t>113.11.97.193:30226</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2428</v>
+        <v>2236.82</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-22 19:15:48</t>
+          <t>2026-03-28 15:41:05</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>неизвестен</t>
+          <t>proxymania</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1.231.81.166:3128</t>
+          <t>185.76.240.43:10001</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2519.03</v>
+        <v>2325.95</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-24 16:40:38</t>
+          <t>2026-03-28 18:27:49</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2211,55 +2236,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>186.148.180.46:999</t>
+          <t>38.145.208.197:8445</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2525.95</v>
+        <v>2428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-03-28 16:49:31</t>
+          <t>2026-03-22 19:15:48</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>неизвестен</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>139.255.94.122:39635</t>
+          <t>1.231.81.166:3128</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2554.06</v>
+        <v>2519.03</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-03-28 18:12:24</t>
+          <t>2026-03-24 16:40:38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2271,11 +2286,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>190.97.236.155:999</t>
+          <t>64.227.76.27:1080</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2573.29</v>
+        <v>2525.52</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2284,37 +2299,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Неизвестно</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-28 16:11:47</t>
+          <t>2026-03-28 14:35:01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>193.233.22.29:10808</t>
+          <t>186.148.180.46:999</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2591.49</v>
+        <v>2525.95</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-28 15:52:24</t>
+          <t>2026-03-28 16:49:31</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2326,11 +2346,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>109.135.16.145:8789</t>
+          <t>139.255.94.122:39635</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2627.64</v>
+        <v>2554.06</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2344,7 +2364,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-28 18:04:33</t>
+          <t>2026-03-28 18:12:24</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2356,11 +2376,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>93.91.112.247:41258</t>
+          <t>190.97.236.155:999</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2659.39</v>
+        <v>2573.29</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2374,37 +2394,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-28 17:41:44</t>
+          <t>2026-03-28 16:11:47</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>rapid_check</t>
+          <t>thespeedx_http</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>200.174.198.32:8888</t>
+          <t>193.233.22.29:10808</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2666.14</v>
+        <v>2591.49</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
+          <t>🇺🇸 США</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 15:52:24</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2416,11 +2431,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>181.78.44.243:999</t>
+          <t>109.135.16.145:8789</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2708.98</v>
+        <v>2627.64</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2434,7 +2449,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:52</t>
+          <t>2026-03-28 18:04:33</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2446,20 +2461,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>103.30.30.5:20326</t>
+          <t>93.91.112.247:41258</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2729.47</v>
+        <v>2659.39</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>🇺🇸 США</t>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-28 16:44:58</t>
+          <t>2026-03-28 17:41:44</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2471,11 +2491,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>212.175.61.26:8080</t>
+          <t>200.174.198.32:8888</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2784.5</v>
+        <v>2666.14</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2489,7 +2509,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-28 18:12:24</t>
+          <t>2026-03-28 16:34:22</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2501,11 +2521,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>43.225.151.174:43030</t>
+          <t>181.78.44.243:999</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2891.33</v>
+        <v>2708.98</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2519,7 +2539,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-28 17:44:16</t>
+          <t>2026-03-28 17:30:52</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2531,11 +2551,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>38.145.220.13:8444</t>
+          <t>103.30.30.5:20326</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2909.32</v>
+        <v>2729.47</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2544,23 +2564,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-28 16:03:06</t>
+          <t>2026-03-28 16:44:58</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>proxymania</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>45.188.167.25:999</t>
+          <t>212.175.61.26:8080</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2913.53</v>
+        <v>2784.5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2574,7 +2594,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-28 16:34:22</t>
+          <t>2026-03-28 18:12:24</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2586,11 +2606,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>38.188.247.12:999</t>
+          <t>43.225.151.174:43030</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2926.76</v>
+        <v>2891.33</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2604,40 +2624,125 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-28 16:06:43</t>
+          <t>2026-03-28 17:44:16</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>thespeedx_http</t>
+          <t>rapid_check</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>38.145.220.13:8444</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2909.32</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>🇺🇸 США</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:03:06</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>proxymania</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>45.188.167.25:999</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2913.53</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:34:22</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>rapid_check</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>38.188.247.12:999</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2926.76</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-03-28 16:06:43</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>thespeedx_http</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>78.134.20.48:8080</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B81" t="n">
         <v>2982.19</v>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>🌎 Другой</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Неизвестно</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>🌎 Другой</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Неизвестно</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>2026-03-28 17:30:52</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>rapid_check</t>
         </is>
@@ -2654,7 +2759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2687,7 +2792,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -2697,7 +2802,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -2745,7 +2850,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -2755,7 +2860,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12"/>
@@ -2773,13 +2878,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Singapore</t>
+          <t xml:space="preserve">  Indonesia</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2789,17 +2894,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Philippines</t>
+          <t xml:space="preserve">  Singapore</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China</t>
+          <t xml:space="preserve">  Philippines</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2809,7 +2914,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Hong Kong</t>
+          <t xml:space="preserve">  Vietnam</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2819,7 +2924,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Indonesia</t>
+          <t xml:space="preserve">  China</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2829,7 +2934,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Germany</t>
+          <t xml:space="preserve">  Hong Kong</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2839,52 +2944,72 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The Netherlands</t>
+          <t xml:space="preserve">  Netherlands</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Germany</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>🕐 ИНФОРМАЦИЯ ОБ ОБНОВЛЕНИИ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Последнее обновление базы</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-28 18:12:24</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  The Netherlands</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Всего проверено за всё время</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>447</v>
+          <t>🕐 ИНФОРМАЦИЯ ОБ ОБНОВЛЕНИИ</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Последнее обновление базы</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:27:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Всего проверено за всё время</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Дата создания отчёта</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-28 18:12:24</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-28 18:27:50</t>
         </is>
       </c>
     </row>
@@ -2942,7 +3067,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
